--- a/population.xlsx
+++ b/population.xlsx
@@ -1,19 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b00e9cd42f584bf2/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Stanting Concept Note\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_049A12A1278F083C140169917EF6D8FD6CAE0400" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40E3B6CE-074C-4C58-8E60-D1FB961F5ED2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Final " sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="120">
   <si>
     <t>Region</t>
   </si>
@@ -377,13 +376,22 @@
   </si>
   <si>
     <t>Alfefshir (አልፈፍሽር)</t>
+  </si>
+  <si>
+    <t>chasga (ቻስጋ)</t>
+  </si>
+  <si>
+    <t>Bentrs) በንተረስ</t>
+  </si>
+  <si>
+    <t>Kokaya (ጎካያ)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,6 +404,21 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="ተቲመ"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="ተቲመ"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="ተቲመ"/>
     </font>
   </fonts>
   <fills count="3">
@@ -412,10 +435,36 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -424,10 +473,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -707,1807 +770,2157 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M55"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="17.44140625" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" customWidth="1"/>
-    <col min="11" max="11" width="26.109375" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.140625" customWidth="1"/>
+    <col min="11" max="11" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" s="2" customFormat="1">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:13" s="2" customFormat="1">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="3">
         <v>5</v>
       </c>
-      <c r="H2" s="2">
-        <v>51150</v>
-      </c>
-      <c r="I2" s="2">
-        <v>8286</v>
-      </c>
-      <c r="J2" s="2">
+      <c r="H2" s="4">
+        <v>7118</v>
+      </c>
+      <c r="I2" s="4">
+        <v>1151</v>
+      </c>
+      <c r="J2" s="3">
         <v>2</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="L2" s="4">
+        <v>1151</v>
+      </c>
+      <c r="M2" s="3">
+        <f>ROUND((SUM(1267*L2)/35362)+0.08,0)</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="2" customFormat="1">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="D3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="3">
         <v>5</v>
       </c>
-      <c r="H3" s="2">
-        <v>51150</v>
-      </c>
-      <c r="I3" s="2">
-        <v>8286</v>
-      </c>
-      <c r="J3" s="2">
+      <c r="H3" s="4">
+        <v>14250</v>
+      </c>
+      <c r="I3" s="4">
+        <v>2305</v>
+      </c>
+      <c r="J3" s="3">
         <v>2</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="L3" s="4">
+        <v>2305</v>
+      </c>
+      <c r="M3" s="3">
+        <f t="shared" ref="M3:M54" si="0">ROUND((SUM(1267*L3)/35362)+0.08,0)</f>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="2" customFormat="1">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="D4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="3">
         <v>5</v>
       </c>
-      <c r="H4" s="2">
-        <v>51150</v>
-      </c>
-      <c r="I4" s="2">
-        <v>8286</v>
-      </c>
-      <c r="J4" s="2">
+      <c r="H4" s="4">
+        <v>2005</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1460</v>
+      </c>
+      <c r="J4" s="3">
         <v>2</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="3" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="L4" s="4">
+        <v>1460</v>
+      </c>
+      <c r="M4" s="3">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="2" customFormat="1">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="D5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="3">
         <v>5</v>
       </c>
-      <c r="H5" s="2">
-        <v>51150</v>
-      </c>
-      <c r="I5" s="2">
-        <v>8286</v>
-      </c>
-      <c r="J5" s="2">
+      <c r="H5" s="4">
+        <v>2274</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1656</v>
+      </c>
+      <c r="J5" s="3">
         <v>2</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="L5" s="4">
+        <v>1656</v>
+      </c>
+      <c r="M5" s="3">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="2" customFormat="1">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="D6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="5">
         <v>44</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="5">
         <v>85148</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="5">
         <v>13794</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="J6" s="5"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="3"/>
+    </row>
+    <row r="7" spans="1:13" s="2" customFormat="1">
+      <c r="A7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="2">
+      <c r="D7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="3">
         <v>30</v>
       </c>
-      <c r="H7" s="2">
-        <v>95447</v>
-      </c>
-      <c r="I7" s="2">
-        <v>15462</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="H7" s="6">
+        <v>2226</v>
+      </c>
+      <c r="I7" s="6">
+        <v>361</v>
+      </c>
+      <c r="J7" s="3">
         <v>6</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="3" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="L7" s="6">
+        <v>361</v>
+      </c>
+      <c r="M7" s="3">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="2" customFormat="1">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="2">
+      <c r="D8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="3">
         <v>30</v>
       </c>
-      <c r="H8" s="2">
-        <v>95447</v>
-      </c>
-      <c r="I8" s="2">
-        <v>15462</v>
-      </c>
-      <c r="J8" s="2">
+      <c r="H8" s="6">
+        <v>2903</v>
+      </c>
+      <c r="I8" s="6">
+        <v>470</v>
+      </c>
+      <c r="J8" s="3">
         <v>6</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="3" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="L8" s="6">
+        <v>470</v>
+      </c>
+      <c r="M8" s="3">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="2" customFormat="1">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="2">
+      <c r="D9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="3">
         <v>30</v>
       </c>
-      <c r="H9" s="2">
-        <v>95447</v>
-      </c>
-      <c r="I9" s="2">
-        <v>15462</v>
-      </c>
-      <c r="J9" s="2">
+      <c r="H9" s="6">
+        <v>1280</v>
+      </c>
+      <c r="I9" s="6">
+        <v>207</v>
+      </c>
+      <c r="J9" s="3">
         <v>6</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="3" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="L9" s="6">
+        <v>207</v>
+      </c>
+      <c r="M9" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="2" customFormat="1">
+      <c r="A10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="2">
+      <c r="D10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="3">
         <v>30</v>
       </c>
-      <c r="H10" s="2">
-        <v>95447</v>
-      </c>
-      <c r="I10" s="2">
-        <v>15462</v>
-      </c>
-      <c r="J10" s="2">
+      <c r="H10" s="6">
+        <v>4841</v>
+      </c>
+      <c r="I10" s="6">
+        <v>784</v>
+      </c>
+      <c r="J10" s="3">
         <v>6</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="3" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="L10" s="6">
+        <v>784</v>
+      </c>
+      <c r="M10" s="3">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="2" customFormat="1">
+      <c r="A11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="2">
+      <c r="D11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="3">
         <v>30</v>
       </c>
-      <c r="H11" s="2">
-        <v>95447</v>
-      </c>
-      <c r="I11" s="2">
-        <v>15462</v>
-      </c>
-      <c r="J11" s="2">
+      <c r="H11" s="6">
+        <v>5400</v>
+      </c>
+      <c r="I11" s="6">
+        <v>874</v>
+      </c>
+      <c r="J11" s="3">
         <v>6</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" s="3" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="L11" s="6">
+        <v>874</v>
+      </c>
+      <c r="M11" s="3">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="2" customFormat="1">
+      <c r="A12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="2">
+      <c r="D12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="3">
         <v>30</v>
       </c>
-      <c r="H12" s="2">
-        <v>95447</v>
-      </c>
-      <c r="I12" s="2">
-        <v>15462</v>
-      </c>
-      <c r="J12" s="2">
+      <c r="H12" s="6">
+        <v>4371</v>
+      </c>
+      <c r="I12" s="6">
+        <v>708</v>
+      </c>
+      <c r="J12" s="3">
         <v>6</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="L12" s="6">
+        <v>708</v>
+      </c>
+      <c r="M12" s="3">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="2" customFormat="1">
+      <c r="A13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="D13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="3">
         <v>37</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="3">
         <v>55983</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="3">
         <v>9069</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" s="2" customFormat="1">
+      <c r="A14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="D14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="3">
         <v>38</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="3">
         <v>73845</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="3">
         <v>11963</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" s="2" customFormat="1">
+      <c r="A15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="D15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="3">
         <v>15</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="3">
         <v>38021</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="3">
         <v>6159</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" s="2" customFormat="1">
+      <c r="A16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="D16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="3">
         <v>23</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="3">
         <v>45722</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="3">
         <v>7407</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="1:13" s="2" customFormat="1">
+      <c r="A17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="D17" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="3">
         <v>19</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="3">
         <v>43153</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="3">
         <v>6991</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="1:13" s="2" customFormat="1">
+      <c r="A18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G18" s="2">
+      <c r="D18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="3">
         <v>19</v>
       </c>
-      <c r="H18" s="2">
-        <v>29261</v>
-      </c>
-      <c r="I18" s="2">
-        <v>4740</v>
-      </c>
-      <c r="J18" s="2">
+      <c r="H18" s="6">
+        <v>1545</v>
+      </c>
+      <c r="I18" s="6">
+        <v>250</v>
+      </c>
+      <c r="J18" s="3">
         <v>4</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="K18" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="L18" s="6">
+        <v>250</v>
+      </c>
+      <c r="M18" s="3">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="2" customFormat="1">
+      <c r="A19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G19" s="2">
+      <c r="D19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="3">
         <v>19</v>
       </c>
-      <c r="H19" s="2">
-        <v>29261</v>
-      </c>
-      <c r="I19" s="2">
-        <v>4740</v>
-      </c>
-      <c r="J19" s="2">
+      <c r="H19" s="6">
+        <v>2057</v>
+      </c>
+      <c r="I19" s="6">
+        <v>333</v>
+      </c>
+      <c r="J19" s="3">
         <v>4</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="K19" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="L19" s="6">
+        <v>333</v>
+      </c>
+      <c r="M19" s="3">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="2" customFormat="1">
+      <c r="A20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="2">
+      <c r="D20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="3">
         <v>19</v>
       </c>
-      <c r="H20" s="2">
-        <v>29261</v>
-      </c>
-      <c r="I20" s="2">
-        <v>4740</v>
-      </c>
-      <c r="J20" s="2">
+      <c r="H20" s="6">
+        <v>1727</v>
+      </c>
+      <c r="I20" s="6">
+        <v>278</v>
+      </c>
+      <c r="J20" s="3">
         <v>4</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="K20" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="L20" s="6">
+        <v>278</v>
+      </c>
+      <c r="M20" s="3">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="2" customFormat="1">
+      <c r="A21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" s="2">
+      <c r="D21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="3">
         <v>19</v>
       </c>
-      <c r="H21" s="2">
-        <v>29261</v>
-      </c>
-      <c r="I21" s="2">
-        <v>4740</v>
-      </c>
-      <c r="J21" s="2">
+      <c r="H21" s="6">
+        <v>1867</v>
+      </c>
+      <c r="I21" s="6">
+        <v>302</v>
+      </c>
+      <c r="J21" s="3">
         <v>4</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="K21" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="L21" s="6">
+        <v>302</v>
+      </c>
+      <c r="M21" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="2" customFormat="1">
+      <c r="A22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G22" s="2">
+      <c r="D22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" s="3">
         <v>10</v>
       </c>
-      <c r="H22" s="2">
-        <v>24642</v>
-      </c>
-      <c r="I22" s="2">
-        <v>3992</v>
-      </c>
-      <c r="J22" s="2">
+      <c r="H22" s="6">
+        <v>1858</v>
+      </c>
+      <c r="I22" s="6">
+        <v>301</v>
+      </c>
+      <c r="J22" s="3">
         <v>3</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="K22" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="L22" s="6">
+        <v>301</v>
+      </c>
+      <c r="M22" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="2" customFormat="1">
+      <c r="A23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G23" s="2">
+      <c r="D23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" s="3">
         <v>10</v>
       </c>
-      <c r="H23" s="2">
-        <v>24642</v>
-      </c>
-      <c r="I23" s="2">
-        <v>3992</v>
-      </c>
-      <c r="J23" s="2">
+      <c r="H23" s="6">
+        <v>2184</v>
+      </c>
+      <c r="I23" s="6">
+        <v>353</v>
+      </c>
+      <c r="J23" s="3">
         <v>3</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="K23" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="L23" s="6">
+        <v>353</v>
+      </c>
+      <c r="M23" s="3">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" s="2" customFormat="1">
+      <c r="A24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G24" s="2">
+      <c r="D24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="3">
         <v>10</v>
       </c>
-      <c r="H24" s="2">
-        <v>24642</v>
-      </c>
-      <c r="I24" s="2">
-        <v>3992</v>
-      </c>
-      <c r="J24" s="2">
+      <c r="H24" s="6">
+        <v>4167</v>
+      </c>
+      <c r="I24" s="6">
+        <v>674</v>
+      </c>
+      <c r="J24" s="3">
         <v>3</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="K24" s="3" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="L24" s="6">
+        <v>674</v>
+      </c>
+      <c r="M24" s="3">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" s="2" customFormat="1">
+      <c r="A25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G25" s="2">
+      <c r="D25" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" s="3">
         <v>22</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="3">
         <v>71256</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" s="3">
         <v>11543</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="2" t="s">
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="1:13" s="2" customFormat="1">
+      <c r="A26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G26" s="2">
+      <c r="D26" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" s="3">
         <v>23</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="7">
+        <v>5938</v>
+      </c>
+      <c r="I26" s="6">
+        <v>962</v>
+      </c>
+      <c r="J26" s="3">
+        <v>4</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="L26" s="6">
+        <v>962</v>
+      </c>
+      <c r="M26" s="3">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="2" customFormat="1">
+      <c r="A27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G27" s="3">
+        <v>23</v>
+      </c>
+      <c r="H27" s="7">
+        <v>3340</v>
+      </c>
+      <c r="I27" s="6">
+        <v>541</v>
+      </c>
+      <c r="J27" s="3">
+        <v>4</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L27" s="6">
+        <v>541</v>
+      </c>
+      <c r="M27" s="3">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" s="2" customFormat="1">
+      <c r="A28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G28" s="3">
+        <v>23</v>
+      </c>
+      <c r="H28" s="3">
         <v>79654</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I28" s="3">
         <v>12904</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J28" s="3">
         <v>4</v>
       </c>
-      <c r="K26" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="K28" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="L28" s="3">
+        <v>12904</v>
+      </c>
+      <c r="M28" s="3">
+        <f t="shared" si="0"/>
+        <v>462</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="2" customFormat="1">
+      <c r="A29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C29" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G27" s="2">
+      <c r="D29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G29" s="3">
         <v>23</v>
       </c>
-      <c r="H27" s="2">
-        <v>79654</v>
-      </c>
-      <c r="I27" s="2">
-        <v>12904</v>
-      </c>
-      <c r="J27" s="2">
+      <c r="H29" s="6">
+        <v>2339</v>
+      </c>
+      <c r="I29" s="6">
+        <v>379</v>
+      </c>
+      <c r="J29" s="3">
         <v>4</v>
       </c>
-      <c r="K27" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="K29" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="L29" s="6">
+        <v>379</v>
+      </c>
+      <c r="M29" s="3">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="2" customFormat="1">
+      <c r="A30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G28" s="2">
-        <v>23</v>
-      </c>
-      <c r="H28" s="2">
-        <v>79654</v>
-      </c>
-      <c r="I28" s="2">
-        <v>12904</v>
-      </c>
-      <c r="J28" s="2">
+      <c r="C30" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" s="3">
+        <v>29</v>
+      </c>
+      <c r="H30" s="3">
+        <v>84872</v>
+      </c>
+      <c r="I30" s="3">
+        <v>13749</v>
+      </c>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="1:13" s="2" customFormat="1">
+      <c r="A31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G31" s="3">
+        <v>17</v>
+      </c>
+      <c r="H31" s="3">
+        <v>26067</v>
+      </c>
+      <c r="I31" s="3">
+        <v>4223</v>
+      </c>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="1:13" s="2" customFormat="1">
+      <c r="A32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G32" s="3">
+        <v>35</v>
+      </c>
+      <c r="H32" s="3">
+        <v>77639</v>
+      </c>
+      <c r="I32" s="3">
+        <v>12577</v>
+      </c>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="1:13" s="2" customFormat="1">
+      <c r="A33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G33" s="3">
+        <v>19</v>
+      </c>
+      <c r="H33" s="6">
+        <v>6610</v>
+      </c>
+      <c r="I33" s="6">
+        <v>1069</v>
+      </c>
+      <c r="J33" s="3">
         <v>4</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="2" t="s">
+      <c r="K33" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="L33" s="6">
+        <v>1069</v>
+      </c>
+      <c r="M33" s="3">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="2" customFormat="1">
+      <c r="A34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G29" s="2">
-        <v>23</v>
-      </c>
-      <c r="H29" s="2">
-        <v>79654</v>
-      </c>
-      <c r="I29" s="2">
-        <v>12904</v>
-      </c>
-      <c r="J29" s="2">
+      <c r="C34" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G34" s="3">
+        <v>19</v>
+      </c>
+      <c r="H34" s="6">
+        <v>2878</v>
+      </c>
+      <c r="I34" s="6">
+        <v>466</v>
+      </c>
+      <c r="J34" s="3">
         <v>4</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="2" t="s">
+      <c r="K34" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L34" s="6">
+        <v>466</v>
+      </c>
+      <c r="M34" s="3">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="2" customFormat="1">
+      <c r="A35" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G30" s="2">
-        <v>29</v>
-      </c>
-      <c r="H30" s="2">
-        <v>84872</v>
-      </c>
-      <c r="I30" s="2">
-        <v>13749</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" s="2" t="s">
+      <c r="C35" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35" s="3">
+        <v>19</v>
+      </c>
+      <c r="H35" s="6">
+        <v>3758</v>
+      </c>
+      <c r="I35" s="6">
+        <v>608</v>
+      </c>
+      <c r="J35" s="3">
+        <v>4</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L35" s="6">
+        <v>608</v>
+      </c>
+      <c r="M35" s="3">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" s="2" customFormat="1">
+      <c r="A36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G31" s="2">
-        <v>17</v>
-      </c>
-      <c r="H31" s="2">
-        <v>26067</v>
-      </c>
-      <c r="I31" s="2">
-        <v>4223</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="2" t="s">
+      <c r="C36" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G36" s="3">
+        <v>19</v>
+      </c>
+      <c r="H36" s="6">
+        <v>3658</v>
+      </c>
+      <c r="I36" s="6">
+        <v>591</v>
+      </c>
+      <c r="J36" s="3">
+        <v>4</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="L36" s="6">
+        <v>591</v>
+      </c>
+      <c r="M36" s="3">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" s="2" customFormat="1">
+      <c r="A37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F32" s="2" t="s">
+      <c r="C37" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G32" s="2">
-        <v>35</v>
-      </c>
-      <c r="H32" s="2">
-        <v>77639</v>
-      </c>
-      <c r="I32" s="2">
-        <v>12577</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="2" t="s">
+      <c r="G37" s="3">
+        <v>36</v>
+      </c>
+      <c r="H37" s="3">
+        <v>104918</v>
+      </c>
+      <c r="I37" s="3">
+        <v>16997</v>
+      </c>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+    </row>
+    <row r="38" spans="1:13" s="2" customFormat="1">
+      <c r="A38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F33" s="2" t="s">
+      <c r="C38" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+    </row>
+    <row r="39" spans="1:13" s="2" customFormat="1">
+      <c r="A39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G39" s="3">
+        <v>19</v>
+      </c>
+      <c r="H39" s="3">
+        <v>31271</v>
+      </c>
+      <c r="I39" s="3">
+        <v>5066</v>
+      </c>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="1:13" s="2" customFormat="1">
+      <c r="A40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G40" s="3">
+        <v>15</v>
+      </c>
+      <c r="H40" s="6">
+        <v>950</v>
+      </c>
+      <c r="I40" s="6">
+        <v>153</v>
+      </c>
+      <c r="J40" s="3">
+        <v>3</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L40" s="6">
+        <v>153</v>
+      </c>
+      <c r="M40" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" s="2" customFormat="1">
+      <c r="A41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G41" s="3">
+        <v>15</v>
+      </c>
+      <c r="H41" s="6">
+        <v>2624</v>
+      </c>
+      <c r="I41" s="6">
+        <v>425</v>
+      </c>
+      <c r="J41" s="3">
+        <v>3</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="L41" s="6">
+        <v>425</v>
+      </c>
+      <c r="M41" s="3">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" s="2" customFormat="1">
+      <c r="A42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G42" s="3">
+        <v>15</v>
+      </c>
+      <c r="H42" s="6">
+        <v>1967</v>
+      </c>
+      <c r="I42" s="6">
+        <v>318</v>
+      </c>
+      <c r="J42" s="3">
+        <v>3</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L42" s="6">
+        <v>318</v>
+      </c>
+      <c r="M42" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" s="2" customFormat="1">
+      <c r="A43" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G43" s="3">
+        <v>12</v>
+      </c>
+      <c r="H43" s="3">
+        <v>52709</v>
+      </c>
+      <c r="I43" s="3">
+        <v>8539</v>
+      </c>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="1:13" s="2" customFormat="1">
+      <c r="A44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G44" s="3">
+        <v>22</v>
+      </c>
+      <c r="H44" s="3">
+        <v>39823</v>
+      </c>
+      <c r="I44" s="3">
+        <v>6451</v>
+      </c>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="1:13" s="2" customFormat="1">
+      <c r="A45" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G45" s="3">
+        <v>15</v>
+      </c>
+      <c r="H45" s="6">
+        <v>1541</v>
+      </c>
+      <c r="I45" s="6">
+        <v>250</v>
+      </c>
+      <c r="J45" s="3">
+        <v>3</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="L45" s="6">
+        <v>250</v>
+      </c>
+      <c r="M45" s="3">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" s="2" customFormat="1">
+      <c r="A46" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G46" s="3">
+        <v>15</v>
+      </c>
+      <c r="H46" s="6">
+        <v>872</v>
+      </c>
+      <c r="I46" s="6">
+        <v>141</v>
+      </c>
+      <c r="J46" s="3">
+        <v>3</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="L46" s="6">
+        <v>141</v>
+      </c>
+      <c r="M46" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" s="2" customFormat="1">
+      <c r="A47" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G47" s="3">
+        <v>15</v>
+      </c>
+      <c r="H47" s="6">
+        <v>3487</v>
+      </c>
+      <c r="I47" s="6">
+        <v>565</v>
+      </c>
+      <c r="J47" s="3">
+        <v>3</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="L47" s="6">
+        <v>565</v>
+      </c>
+      <c r="M47" s="3">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" s="2" customFormat="1">
+      <c r="A48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F48" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="2">
-        <v>19</v>
-      </c>
-      <c r="H33" s="2">
-        <v>79602</v>
-      </c>
-      <c r="I33" s="2">
-        <v>12896</v>
-      </c>
-      <c r="J33" s="2">
+      <c r="G48" s="3">
+        <v>34</v>
+      </c>
+      <c r="H48" s="6">
+        <v>3933</v>
+      </c>
+      <c r="I48" s="9">
+        <v>654</v>
+      </c>
+      <c r="J48" s="3">
+        <v>7</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L48" s="9">
+        <v>654</v>
+      </c>
+      <c r="M48" s="3">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" s="2" customFormat="1">
+      <c r="A49" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G49" s="3">
+        <v>34</v>
+      </c>
+      <c r="H49" s="6">
+        <v>7519</v>
+      </c>
+      <c r="I49" s="6">
+        <v>1249</v>
+      </c>
+      <c r="J49" s="3">
+        <v>7</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L49" s="6">
+        <v>1249</v>
+      </c>
+      <c r="M49" s="3">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" s="2" customFormat="1">
+      <c r="A50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G50" s="3">
+        <v>34</v>
+      </c>
+      <c r="H50" s="6">
+        <v>4245</v>
+      </c>
+      <c r="I50" s="6">
+        <v>705</v>
+      </c>
+      <c r="J50" s="3">
+        <v>7</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="L50" s="6">
+        <v>705</v>
+      </c>
+      <c r="M50" s="3">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" s="2" customFormat="1">
+      <c r="A51" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G51" s="3">
+        <v>34</v>
+      </c>
+      <c r="H51" s="6">
+        <v>736</v>
+      </c>
+      <c r="I51" s="6">
+        <v>122</v>
+      </c>
+      <c r="J51" s="3">
+        <v>7</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L51" s="6">
+        <v>122</v>
+      </c>
+      <c r="M51" s="3">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F34" s="2" t="s">
+    </row>
+    <row r="52" spans="1:13" s="2" customFormat="1">
+      <c r="A52" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G34" s="2">
-        <v>19</v>
-      </c>
-      <c r="H34" s="2">
-        <v>79602</v>
-      </c>
-      <c r="I34" s="2">
-        <v>12896</v>
-      </c>
-      <c r="J34" s="2">
-        <v>4</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="G52" s="3">
+        <v>34</v>
+      </c>
+      <c r="H52" s="6">
+        <v>832</v>
+      </c>
+      <c r="I52" s="6">
+        <v>138</v>
+      </c>
+      <c r="J52" s="3">
+        <v>7</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L52" s="6">
+        <v>138</v>
+      </c>
+      <c r="M52" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" s="2" customFormat="1">
+      <c r="A53" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G35" s="2">
-        <v>19</v>
-      </c>
-      <c r="H35" s="2">
-        <v>79602</v>
-      </c>
-      <c r="I35" s="2">
-        <v>12896</v>
-      </c>
-      <c r="J35" s="2">
-        <v>4</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F36" s="2" t="s">
+      <c r="G53" s="3">
+        <v>34</v>
+      </c>
+      <c r="H53" s="6">
+        <v>2982</v>
+      </c>
+      <c r="I53" s="6">
+        <v>495</v>
+      </c>
+      <c r="J53" s="3">
+        <v>7</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L53" s="6">
+        <v>495</v>
+      </c>
+      <c r="M53" s="3">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" s="2" customFormat="1">
+      <c r="A54" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F54" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G36" s="2">
-        <v>19</v>
-      </c>
-      <c r="H36" s="2">
-        <v>79602</v>
-      </c>
-      <c r="I36" s="2">
-        <v>12896</v>
-      </c>
-      <c r="J36" s="2">
-        <v>4</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G37" s="2">
-        <v>36</v>
-      </c>
-      <c r="H37" s="2">
-        <v>104918</v>
-      </c>
-      <c r="I37" s="2">
-        <v>16997</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G39" s="2">
-        <v>19</v>
-      </c>
-      <c r="H39" s="2">
-        <v>31271</v>
-      </c>
-      <c r="I39" s="2">
-        <v>5066</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G40" s="2">
-        <v>15</v>
-      </c>
-      <c r="H40" s="2">
-        <v>22290</v>
-      </c>
-      <c r="I40" s="2">
-        <v>3610</v>
-      </c>
-      <c r="J40" s="2">
-        <v>3</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G41" s="2">
-        <v>15</v>
-      </c>
-      <c r="H41" s="2">
-        <v>22290</v>
-      </c>
-      <c r="I41" s="2">
-        <v>3610</v>
-      </c>
-      <c r="J41" s="2">
-        <v>3</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G42" s="2">
-        <v>15</v>
-      </c>
-      <c r="H42" s="2">
-        <v>22290</v>
-      </c>
-      <c r="I42" s="2">
-        <v>3610</v>
-      </c>
-      <c r="J42" s="2">
-        <v>3</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G43" s="2">
-        <v>12</v>
-      </c>
-      <c r="H43" s="2">
-        <v>52709</v>
-      </c>
-      <c r="I43" s="2">
-        <v>8539</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G44" s="2">
-        <v>22</v>
-      </c>
-      <c r="H44" s="2">
-        <v>39823</v>
-      </c>
-      <c r="I44" s="2">
-        <v>6451</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G45" s="2">
-        <v>15</v>
-      </c>
-      <c r="H45" s="2">
-        <v>31468</v>
-      </c>
-      <c r="I45" s="2">
-        <v>5098</v>
-      </c>
-      <c r="J45" s="2">
-        <v>3</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G46" s="2">
-        <v>15</v>
-      </c>
-      <c r="H46" s="2">
-        <v>31468</v>
-      </c>
-      <c r="I46" s="2">
-        <v>5098</v>
-      </c>
-      <c r="J46" s="2">
-        <v>3</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G47" s="2">
-        <v>15</v>
-      </c>
-      <c r="H47" s="2">
-        <v>31468</v>
-      </c>
-      <c r="I47" s="2">
-        <v>5098</v>
-      </c>
-      <c r="J47" s="2">
-        <v>3</v>
-      </c>
-      <c r="K47" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G48" s="2">
-        <v>34</v>
-      </c>
-      <c r="H48" s="2">
-        <v>87539</v>
-      </c>
-      <c r="I48" s="2">
-        <v>14181</v>
-      </c>
-      <c r="J48" s="2">
-        <v>7</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G49" s="2">
-        <v>34</v>
-      </c>
-      <c r="H49" s="2">
-        <v>87539</v>
-      </c>
-      <c r="I49" s="2">
-        <v>14181</v>
-      </c>
-      <c r="J49" s="2">
-        <v>7</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G50" s="2">
-        <v>34</v>
-      </c>
-      <c r="H50" s="2">
-        <v>87539</v>
-      </c>
-      <c r="I50" s="2">
-        <v>14181</v>
-      </c>
-      <c r="J50" s="2">
-        <v>7</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G51" s="2">
-        <v>34</v>
-      </c>
-      <c r="H51" s="2">
-        <v>87539</v>
-      </c>
-      <c r="I51" s="2">
-        <v>14181</v>
-      </c>
-      <c r="J51" s="2">
-        <v>7</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G52" s="2">
-        <v>34</v>
-      </c>
-      <c r="H52" s="2">
-        <v>87539</v>
-      </c>
-      <c r="I52" s="2">
-        <v>14181</v>
-      </c>
-      <c r="J52" s="2">
-        <v>7</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G53" s="2">
-        <v>34</v>
-      </c>
-      <c r="H53" s="2">
-        <v>87539</v>
-      </c>
-      <c r="I53" s="2">
-        <v>14181</v>
-      </c>
-      <c r="J53" s="2">
-        <v>7</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G54" s="2">
-        <v>34</v>
-      </c>
-      <c r="H54" s="2">
-        <v>87539</v>
-      </c>
-      <c r="I54" s="2">
-        <v>14181</v>
-      </c>
-      <c r="J54" s="2">
-        <v>7</v>
-      </c>
-      <c r="K54" s="2" t="s">
+      <c r="G54" s="3">
+        <v>34</v>
+      </c>
+      <c r="H54" s="6">
+        <v>960</v>
+      </c>
+      <c r="I54" s="6">
+        <v>160</v>
+      </c>
+      <c r="J54" s="3">
+        <v>7</v>
+      </c>
+      <c r="K54" s="3" t="s">
         <v>71</v>
+      </c>
+      <c r="L54" s="6">
+        <v>160</v>
+      </c>
+      <c r="M54" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
+      <c r="L55">
+        <f>SUM(L2:L54)</f>
+        <v>35362</v>
+      </c>
+      <c r="M55" s="10">
+        <f>SUM(M2:M54)</f>
+        <v>1267</v>
       </c>
     </row>
   </sheetData>
@@ -2516,26 +2929,26 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M56"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2576,7 +2989,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2611,7 +3024,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -2646,7 +3059,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" s="1" customFormat="1">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -2681,7 +3094,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" s="1" customFormat="1">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -2716,7 +3129,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2745,7 +3158,7 @@
         <v>13794</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -2774,7 +3187,7 @@
         <v>15462</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2803,7 +3216,7 @@
         <v>9069</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" s="1" customFormat="1">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -2838,7 +3251,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" s="1" customFormat="1">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -2873,7 +3286,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" s="1" customFormat="1">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -2908,7 +3321,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" s="1" customFormat="1">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -2943,7 +3356,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" s="1" customFormat="1">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
@@ -2978,7 +3391,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" s="1" customFormat="1">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -3013,7 +3426,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" s="1" customFormat="1">
       <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
@@ -3048,7 +3461,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" s="1" customFormat="1">
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
@@ -3083,7 +3496,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -3112,7 +3525,7 @@
         <v>6159</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -3141,7 +3554,7 @@
         <v>7407</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -3170,7 +3583,7 @@
         <v>6991</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" s="1" customFormat="1">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -3205,7 +3618,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" s="1" customFormat="1">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
@@ -3240,7 +3653,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" s="1" customFormat="1">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -3275,7 +3688,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" s="1" customFormat="1">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
@@ -3310,7 +3723,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" s="1" customFormat="1">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
@@ -3345,7 +3758,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" s="1" customFormat="1">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
@@ -3380,7 +3793,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" s="1" customFormat="1">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
@@ -3415,7 +3828,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -3444,7 +3857,7 @@
         <v>11543</v>
       </c>
     </row>
-    <row r="28" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" s="1" customFormat="1">
       <c r="A28" s="1" t="s">
         <v>7</v>
       </c>
@@ -3479,7 +3892,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" s="1" customFormat="1">
       <c r="A29" s="1" t="s">
         <v>7</v>
       </c>
@@ -3514,7 +3927,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" s="1" customFormat="1">
       <c r="A30" s="1" t="s">
         <v>7</v>
       </c>
@@ -3549,7 +3962,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" s="1" customFormat="1">
       <c r="A31" s="1" t="s">
         <v>7</v>
       </c>
@@ -3584,7 +3997,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -3613,7 +4026,7 @@
         <v>13749</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -3642,7 +4055,7 @@
         <v>4223</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11">
       <c r="A34" t="s">
         <v>7</v>
       </c>
@@ -3671,7 +4084,7 @@
         <v>12577</v>
       </c>
     </row>
-    <row r="35" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" s="1" customFormat="1">
       <c r="A35" s="1" t="s">
         <v>7</v>
       </c>
@@ -3706,7 +4119,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" s="1" customFormat="1">
       <c r="A36" s="1" t="s">
         <v>7</v>
       </c>
@@ -3741,7 +4154,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" s="1" customFormat="1">
       <c r="A37" s="1" t="s">
         <v>7</v>
       </c>
@@ -3776,7 +4189,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" s="1" customFormat="1">
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
@@ -3811,7 +4224,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11">
       <c r="A39" t="s">
         <v>7</v>
       </c>
@@ -3840,7 +4253,7 @@
         <v>16997</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -3857,7 +4270,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11">
       <c r="A41" t="s">
         <v>7</v>
       </c>
@@ -3886,7 +4299,7 @@
         <v>5066</v>
       </c>
     </row>
-    <row r="42" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" s="1" customFormat="1">
       <c r="A42" s="1" t="s">
         <v>7</v>
       </c>
@@ -3921,7 +4334,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" s="1" customFormat="1">
       <c r="A43" s="1" t="s">
         <v>7</v>
       </c>
@@ -3956,7 +4369,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" s="1" customFormat="1">
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
@@ -3991,7 +4404,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11">
       <c r="A45" t="s">
         <v>7</v>
       </c>
@@ -4020,7 +4433,7 @@
         <v>8539</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -4049,7 +4462,7 @@
         <v>6451</v>
       </c>
     </row>
-    <row r="47" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" s="1" customFormat="1">
       <c r="A47" s="1" t="s">
         <v>7</v>
       </c>
@@ -4084,7 +4497,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="48" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" s="1" customFormat="1">
       <c r="A48" s="1" t="s">
         <v>7</v>
       </c>
@@ -4119,7 +4532,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" s="1" customFormat="1">
       <c r="A49" s="1" t="s">
         <v>7</v>
       </c>
@@ -4154,7 +4567,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="50" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" s="1" customFormat="1">
       <c r="A50" s="1" t="s">
         <v>7</v>
       </c>
@@ -4189,7 +4602,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" s="1" customFormat="1">
       <c r="A51" s="1" t="s">
         <v>7</v>
       </c>
@@ -4224,7 +4637,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="52" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" s="1" customFormat="1">
       <c r="A52" s="1" t="s">
         <v>7</v>
       </c>
@@ -4259,7 +4672,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" s="1" customFormat="1">
       <c r="A53" s="1" t="s">
         <v>7</v>
       </c>
@@ -4294,7 +4707,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" s="1" customFormat="1">
       <c r="A54" s="1" t="s">
         <v>7</v>
       </c>
@@ -4329,7 +4742,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="55" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" s="1" customFormat="1">
       <c r="A55" s="1" t="s">
         <v>7</v>
       </c>
@@ -4364,7 +4777,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="56" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" s="1" customFormat="1">
       <c r="A56" s="1" t="s">
         <v>7</v>
       </c>
@@ -4400,7 +4813,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:N57">
+  <sortState ref="A4:N57">
     <sortCondition ref="B1:B57"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/population.xlsx
+++ b/population.xlsx
@@ -1,24 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Stanting Concept Note\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b00e9cd42f584bf2/Documents/Population visualizer/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{902D0A46-30B1-4E0E-BEEA-BF2A24C7BFC4}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Final " sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -390,7 +400,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -473,24 +483,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -770,2158 +778,2151 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M55"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.140625" customWidth="1"/>
-    <col min="11" max="11" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.109375" customWidth="1"/>
+    <col min="11" max="11" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="D1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="2" customFormat="1">
-      <c r="A2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="1:13">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="D2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>5</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="3">
         <v>7118</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="3">
         <v>1151</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="2">
         <v>2</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="3">
         <v>1151</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="2">
         <f>ROUND((SUM(1267*L2)/35362)+0.08,0)</f>
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="2" customFormat="1">
-      <c r="A3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="3" spans="1:13">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="D3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>5</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="3">
         <v>14250</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="3">
         <v>2305</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>2</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="3">
         <v>2305</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="2">
         <f t="shared" ref="M3:M54" si="0">ROUND((SUM(1267*L3)/35362)+0.08,0)</f>
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="2" customFormat="1">
-      <c r="A4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:13">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="D4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>5</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="3">
         <v>2005</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="3">
         <v>1460</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <v>2</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="3">
         <v>1460</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="2">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="2" customFormat="1">
-      <c r="A5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:13">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="D5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>5</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="3">
         <v>2274</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="3">
         <v>1656</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <v>2</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="3">
         <v>1656</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="2">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="2" customFormat="1">
-      <c r="A6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="5" t="s">
+    <row r="6" spans="1:13">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="D6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="4">
         <v>44</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>85148</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="4">
         <v>13794</v>
       </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="3"/>
-    </row>
-    <row r="7" spans="1:13" s="2" customFormat="1">
-      <c r="A7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="J6" s="4"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="3">
+      <c r="D7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="2">
         <v>30</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>2226</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>361</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <v>6</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <v>361</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="2" customFormat="1">
-      <c r="A8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:13">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="D8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="2">
         <v>30</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>2903</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <v>470</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="2">
         <v>6</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="5">
         <v>470</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="2" customFormat="1">
-      <c r="A9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:13">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="D9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="2">
         <v>30</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>1280</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="5">
         <v>207</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
         <v>6</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="5">
         <v>207</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="2" customFormat="1">
-      <c r="A10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:13">
+      <c r="A10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="D10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="2">
         <v>30</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>4841</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="5">
         <v>784</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="2">
         <v>6</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <v>784</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="2" customFormat="1">
-      <c r="A11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:13">
+      <c r="A11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="3">
+      <c r="D11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="2">
         <v>30</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <v>5400</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="5">
         <v>874</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
         <v>6</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="5">
         <v>874</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="2" customFormat="1">
-      <c r="A12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:13">
+      <c r="A12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="D12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="2">
         <v>30</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>4371</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="5">
         <v>708</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="2">
         <v>6</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="K12" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <v>708</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" s="2" customFormat="1">
-      <c r="A13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:13">
+      <c r="A13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="D13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <v>37</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <v>55983</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="2">
         <v>9069</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" s="2" customFormat="1">
-      <c r="A14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="D14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
         <v>38</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="2">
         <v>73845</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="2">
         <v>11963</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" s="2" customFormat="1">
-      <c r="A15" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="D15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <v>15</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <v>38021</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="2">
         <v>6159</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" s="2" customFormat="1">
-      <c r="A16" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="D16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
         <v>23</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <v>45722</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="2">
         <v>7407</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="1:13" s="2" customFormat="1">
-      <c r="A17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="D17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="2">
         <v>19</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="2">
         <v>43153</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="2">
         <v>6991</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="1:13" s="2" customFormat="1">
-      <c r="A18" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="D18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="2">
         <v>19</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="5">
         <v>1545</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="5">
         <v>250</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="2">
         <v>4</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="K18" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="5">
         <v>250</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:13" s="2" customFormat="1">
-      <c r="A19" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="1:13">
+      <c r="A19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G19" s="3">
+      <c r="D19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="2">
         <v>19</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="5">
         <v>2057</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="5">
         <v>333</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="2">
         <v>4</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="K19" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="5">
         <v>333</v>
       </c>
-      <c r="M19" s="3">
+      <c r="M19" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:13" s="2" customFormat="1">
-      <c r="A20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="1:13">
+      <c r="A20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="D20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="2">
         <v>19</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="5">
         <v>1727</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="5">
         <v>278</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="2">
         <v>4</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="K20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="5">
         <v>278</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:13" s="2" customFormat="1">
-      <c r="A21" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="1:13">
+      <c r="A21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="D21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="2">
         <v>19</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="5">
         <v>1867</v>
       </c>
-      <c r="I21" s="6">
+      <c r="I21" s="5">
         <v>302</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="2">
         <v>4</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="K21" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="5">
         <v>302</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:13" s="2" customFormat="1">
-      <c r="A22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="1:13">
+      <c r="A22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="D22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" s="2">
         <v>10</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="5">
         <v>1858</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="5">
         <v>301</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="2">
         <v>3</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="K22" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L22" s="6">
+      <c r="L22" s="5">
         <v>301</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:13" s="2" customFormat="1">
-      <c r="A23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="1:13">
+      <c r="A23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="D23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" s="2">
         <v>10</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="5">
         <v>2184</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="5">
         <v>353</v>
       </c>
-      <c r="J23" s="3">
+      <c r="J23" s="2">
         <v>3</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="K23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="5">
         <v>353</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:13" s="2" customFormat="1">
-      <c r="A24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="1:13">
+      <c r="A24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="D24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="2">
         <v>10</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="5">
         <v>4167</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="5">
         <v>674</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24" s="2">
         <v>3</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="K24" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="L24" s="6">
+      <c r="L24" s="5">
         <v>674</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:13" s="2" customFormat="1">
-      <c r="A25" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="1:13">
+      <c r="A25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G25" s="3">
+      <c r="D25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" s="2">
         <v>22</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25" s="2">
         <v>71256</v>
       </c>
-      <c r="I25" s="3">
+      <c r="I25" s="2">
         <v>11543</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="1:13" s="2" customFormat="1">
-      <c r="A26" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="D26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" s="2">
         <v>23</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="6">
         <v>5938</v>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="5">
         <v>962</v>
       </c>
-      <c r="J26" s="3">
+      <c r="J26" s="2">
         <v>4</v>
       </c>
-      <c r="K26" s="3" t="s">
+      <c r="K26" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="5">
         <v>962</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="2" customFormat="1">
-      <c r="A27" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="3" t="s">
+    <row r="27" spans="1:13">
+      <c r="A27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="D27" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G27" s="2">
         <v>23</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="6">
         <v>3340</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I27" s="5">
         <v>541</v>
       </c>
-      <c r="J27" s="3">
+      <c r="J27" s="2">
         <v>4</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="K27" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="5">
         <v>541</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:13" s="2" customFormat="1">
-      <c r="A28" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="1:13">
+      <c r="A28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G28" s="3">
+      <c r="D28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G28" s="2">
         <v>23</v>
       </c>
-      <c r="H28" s="3">
+      <c r="H28" s="2">
         <v>79654</v>
       </c>
-      <c r="I28" s="3">
+      <c r="I28" s="2">
         <v>12904</v>
       </c>
-      <c r="J28" s="3">
+      <c r="J28" s="2">
         <v>4</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="K28" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="L28" s="3">
+      <c r="L28" s="2">
         <v>12904</v>
       </c>
-      <c r="M28" s="3">
+      <c r="M28" s="2">
         <f t="shared" si="0"/>
         <v>462</v>
       </c>
     </row>
-    <row r="29" spans="1:13" s="2" customFormat="1">
-      <c r="A29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="1:13">
+      <c r="A29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G29" s="3">
+      <c r="D29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G29" s="2">
         <v>23</v>
       </c>
-      <c r="H29" s="6">
+      <c r="H29" s="5">
         <v>2339</v>
       </c>
-      <c r="I29" s="6">
+      <c r="I29" s="5">
         <v>379</v>
       </c>
-      <c r="J29" s="3">
+      <c r="J29" s="2">
         <v>4</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="K29" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="5">
         <v>379</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M29" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:13" s="2" customFormat="1">
-      <c r="A30" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="1:13">
+      <c r="A30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="D30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="2">
         <v>29</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30" s="2">
         <v>84872</v>
       </c>
-      <c r="I30" s="3">
+      <c r="I30" s="2">
         <v>13749</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="1:13" s="2" customFormat="1">
-      <c r="A31" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" s="3" t="s">
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G31" s="3">
+      <c r="D31" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G31" s="2">
         <v>17</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H31" s="2">
         <v>26067</v>
       </c>
-      <c r="I31" s="3">
+      <c r="I31" s="2">
         <v>4223</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="1:13" s="2" customFormat="1">
-      <c r="A32" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="3" t="s">
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="D32" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G32" s="3">
-        <v>35</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="G32" s="2">
+        <v>35</v>
+      </c>
+      <c r="H32" s="2">
         <v>77639</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="2">
         <v>12577</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="1:13" s="2" customFormat="1">
-      <c r="A33" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="3" t="s">
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F33" s="3" t="s">
+      <c r="D33" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="2">
         <v>19</v>
       </c>
-      <c r="H33" s="6">
+      <c r="H33" s="5">
         <v>6610</v>
       </c>
-      <c r="I33" s="6">
+      <c r="I33" s="5">
         <v>1069</v>
       </c>
-      <c r="J33" s="3">
+      <c r="J33" s="2">
         <v>4</v>
       </c>
-      <c r="K33" s="3" t="s">
+      <c r="K33" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="L33" s="6">
+      <c r="L33" s="5">
         <v>1069</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:13" s="2" customFormat="1">
-      <c r="A34" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="3" t="s">
+    <row r="34" spans="1:13">
+      <c r="A34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F34" s="3" t="s">
+      <c r="D34" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="2">
         <v>19</v>
       </c>
-      <c r="H34" s="6">
+      <c r="H34" s="5">
         <v>2878</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="5">
         <v>466</v>
       </c>
-      <c r="J34" s="3">
+      <c r="J34" s="2">
         <v>4</v>
       </c>
-      <c r="K34" s="3" t="s">
+      <c r="K34" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="L34" s="6">
+      <c r="L34" s="5">
         <v>466</v>
       </c>
-      <c r="M34" s="3">
+      <c r="M34" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:13" s="2" customFormat="1">
-      <c r="A35" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" s="3" t="s">
+    <row r="35" spans="1:13">
+      <c r="A35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F35" s="3" t="s">
+      <c r="D35" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="2">
         <v>19</v>
       </c>
-      <c r="H35" s="6">
+      <c r="H35" s="5">
         <v>3758</v>
       </c>
-      <c r="I35" s="6">
+      <c r="I35" s="5">
         <v>608</v>
       </c>
-      <c r="J35" s="3">
+      <c r="J35" s="2">
         <v>4</v>
       </c>
-      <c r="K35" s="3" t="s">
+      <c r="K35" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L35" s="6">
+      <c r="L35" s="5">
         <v>608</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:13" s="2" customFormat="1">
-      <c r="A36" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" s="3" t="s">
+    <row r="36" spans="1:13">
+      <c r="A36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F36" s="3" t="s">
+      <c r="D36" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="2">
         <v>19</v>
       </c>
-      <c r="H36" s="6">
+      <c r="H36" s="5">
         <v>3658</v>
       </c>
-      <c r="I36" s="6">
+      <c r="I36" s="5">
         <v>591</v>
       </c>
-      <c r="J36" s="3">
+      <c r="J36" s="2">
         <v>4</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="K36" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="L36" s="6">
+      <c r="L36" s="5">
         <v>591</v>
       </c>
-      <c r="M36" s="3">
+      <c r="M36" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="2" customFormat="1">
-      <c r="A37" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" s="3" t="s">
+    <row r="37" spans="1:13">
+      <c r="A37" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F37" s="3" t="s">
+      <c r="D37" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G37" s="3">
-        <v>36</v>
-      </c>
-      <c r="H37" s="3">
+      <c r="G37" s="2">
+        <v>36</v>
+      </c>
+      <c r="H37" s="2">
         <v>104918</v>
       </c>
-      <c r="I37" s="3">
+      <c r="I37" s="2">
         <v>16997</v>
       </c>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-    </row>
-    <row r="38" spans="1:13" s="2" customFormat="1">
-      <c r="A38" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" s="3" t="s">
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-    </row>
-    <row r="39" spans="1:13" s="2" customFormat="1">
-      <c r="A39" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" s="3" t="s">
+      <c r="D38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G39" s="3">
+      <c r="D39" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G39" s="2">
         <v>19</v>
       </c>
-      <c r="H39" s="3">
+      <c r="H39" s="2">
         <v>31271</v>
       </c>
-      <c r="I39" s="3">
+      <c r="I39" s="2">
         <v>5066</v>
       </c>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="1:13" s="2" customFormat="1">
-      <c r="A40" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" s="3" t="s">
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G40" s="3">
+      <c r="D40" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G40" s="2">
         <v>15</v>
       </c>
-      <c r="H40" s="6">
+      <c r="H40" s="5">
         <v>950</v>
       </c>
-      <c r="I40" s="6">
+      <c r="I40" s="5">
         <v>153</v>
       </c>
-      <c r="J40" s="3">
+      <c r="J40" s="2">
         <v>3</v>
       </c>
-      <c r="K40" s="3" t="s">
+      <c r="K40" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="L40" s="6">
+      <c r="L40" s="5">
         <v>153</v>
       </c>
-      <c r="M40" s="3">
+      <c r="M40" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:13" s="2" customFormat="1">
-      <c r="A41" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" s="3" t="s">
+    <row r="41" spans="1:13">
+      <c r="A41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="D41" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G41" s="2">
         <v>15</v>
       </c>
-      <c r="H41" s="6">
+      <c r="H41" s="5">
         <v>2624</v>
       </c>
-      <c r="I41" s="6">
+      <c r="I41" s="5">
         <v>425</v>
       </c>
-      <c r="J41" s="3">
+      <c r="J41" s="2">
         <v>3</v>
       </c>
-      <c r="K41" s="3" t="s">
+      <c r="K41" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="L41" s="6">
+      <c r="L41" s="5">
         <v>425</v>
       </c>
-      <c r="M41" s="3">
+      <c r="M41" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:13" s="2" customFormat="1">
-      <c r="A42" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B42" s="3" t="s">
+    <row r="42" spans="1:13">
+      <c r="A42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="D42" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G42" s="2">
         <v>15</v>
       </c>
-      <c r="H42" s="6">
+      <c r="H42" s="5">
         <v>1967</v>
       </c>
-      <c r="I42" s="6">
+      <c r="I42" s="5">
         <v>318</v>
       </c>
-      <c r="J42" s="3">
+      <c r="J42" s="2">
         <v>3</v>
       </c>
-      <c r="K42" s="3" t="s">
+      <c r="K42" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L42" s="6">
+      <c r="L42" s="5">
         <v>318</v>
       </c>
-      <c r="M42" s="3">
+      <c r="M42" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:13" s="2" customFormat="1">
-      <c r="A43" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B43" s="3" t="s">
+    <row r="43" spans="1:13">
+      <c r="A43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="D43" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G43" s="2">
         <v>12</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="2">
         <v>52709</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="2">
         <v>8539</v>
       </c>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="1:13" s="2" customFormat="1">
-      <c r="A44" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="D44" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G44" s="2">
         <v>22</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="2">
         <v>39823</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="2">
         <v>6451</v>
       </c>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="1:13" s="2" customFormat="1">
-      <c r="A45" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B45" s="3" t="s">
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="D45" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G45" s="2">
         <v>15</v>
       </c>
-      <c r="H45" s="6">
+      <c r="H45" s="5">
         <v>1541</v>
       </c>
-      <c r="I45" s="6">
+      <c r="I45" s="5">
         <v>250</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="2">
         <v>3</v>
       </c>
-      <c r="K45" s="8" t="s">
+      <c r="K45" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="L45" s="6">
+      <c r="L45" s="5">
         <v>250</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:13" s="2" customFormat="1">
-      <c r="A46" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" s="3" t="s">
+    <row r="46" spans="1:13">
+      <c r="A46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="D46" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G46" s="2">
         <v>15</v>
       </c>
-      <c r="H46" s="6">
+      <c r="H46" s="5">
         <v>872</v>
       </c>
-      <c r="I46" s="6">
+      <c r="I46" s="5">
         <v>141</v>
       </c>
-      <c r="J46" s="3">
+      <c r="J46" s="2">
         <v>3</v>
       </c>
-      <c r="K46" s="4" t="s">
+      <c r="K46" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="L46" s="6">
+      <c r="L46" s="5">
         <v>141</v>
       </c>
-      <c r="M46" s="3">
+      <c r="M46" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:13" s="2" customFormat="1">
-      <c r="A47" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B47" s="3" t="s">
+    <row r="47" spans="1:13">
+      <c r="A47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="D47" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G47" s="2">
         <v>15</v>
       </c>
-      <c r="H47" s="6">
+      <c r="H47" s="5">
         <v>3487</v>
       </c>
-      <c r="I47" s="6">
+      <c r="I47" s="5">
         <v>565</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="2">
         <v>3</v>
       </c>
-      <c r="K47" s="8" t="s">
+      <c r="K47" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="L47" s="6">
+      <c r="L47" s="5">
         <v>565</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:13" s="2" customFormat="1">
-      <c r="A48" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" s="3" t="s">
+    <row r="48" spans="1:13">
+      <c r="A48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F48" s="3" t="s">
+      <c r="D48" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G48" s="3">
-        <v>34</v>
-      </c>
-      <c r="H48" s="6">
+      <c r="G48" s="2">
+        <v>34</v>
+      </c>
+      <c r="H48" s="5">
         <v>3933</v>
       </c>
-      <c r="I48" s="9">
+      <c r="I48" s="7">
         <v>654</v>
       </c>
-      <c r="J48" s="3">
-        <v>7</v>
-      </c>
-      <c r="K48" s="3" t="s">
+      <c r="J48" s="2">
+        <v>7</v>
+      </c>
+      <c r="K48" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="L48" s="9">
+      <c r="L48" s="7">
         <v>654</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:13" s="2" customFormat="1">
-      <c r="A49" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B49" s="3" t="s">
+    <row r="49" spans="1:13">
+      <c r="A49" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F49" s="3" t="s">
+      <c r="D49" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F49" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G49" s="3">
-        <v>34</v>
-      </c>
-      <c r="H49" s="6">
+      <c r="G49" s="2">
+        <v>34</v>
+      </c>
+      <c r="H49" s="5">
         <v>7519</v>
       </c>
-      <c r="I49" s="6">
+      <c r="I49" s="5">
         <v>1249</v>
       </c>
-      <c r="J49" s="3">
-        <v>7</v>
-      </c>
-      <c r="K49" s="3" t="s">
+      <c r="J49" s="2">
+        <v>7</v>
+      </c>
+      <c r="K49" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="L49" s="6">
+      <c r="L49" s="5">
         <v>1249</v>
       </c>
-      <c r="M49" s="3">
+      <c r="M49" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
     </row>
-    <row r="50" spans="1:13" s="2" customFormat="1">
-      <c r="A50" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B50" s="3" t="s">
+    <row r="50" spans="1:13">
+      <c r="A50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F50" s="3" t="s">
+      <c r="D50" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G50" s="3">
-        <v>34</v>
-      </c>
-      <c r="H50" s="6">
+      <c r="G50" s="2">
+        <v>34</v>
+      </c>
+      <c r="H50" s="5">
         <v>4245</v>
       </c>
-      <c r="I50" s="6">
+      <c r="I50" s="5">
         <v>705</v>
       </c>
-      <c r="J50" s="3">
-        <v>7</v>
-      </c>
-      <c r="K50" s="3" t="s">
+      <c r="J50" s="2">
+        <v>7</v>
+      </c>
+      <c r="K50" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="L50" s="6">
+      <c r="L50" s="5">
         <v>705</v>
       </c>
-      <c r="M50" s="3">
+      <c r="M50" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:13" s="2" customFormat="1">
-      <c r="A51" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B51" s="3" t="s">
+    <row r="51" spans="1:13">
+      <c r="A51" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F51" s="3" t="s">
+      <c r="D51" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G51" s="3">
-        <v>34</v>
-      </c>
-      <c r="H51" s="6">
+      <c r="G51" s="2">
+        <v>34</v>
+      </c>
+      <c r="H51" s="5">
         <v>736</v>
       </c>
-      <c r="I51" s="6">
+      <c r="I51" s="5">
         <v>122</v>
       </c>
-      <c r="J51" s="3">
-        <v>7</v>
-      </c>
-      <c r="K51" s="3" t="s">
+      <c r="J51" s="2">
+        <v>7</v>
+      </c>
+      <c r="K51" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L51" s="6">
+      <c r="L51" s="5">
         <v>122</v>
       </c>
-      <c r="M51" s="3">
+      <c r="M51" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:13" s="2" customFormat="1">
-      <c r="A52" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B52" s="3" t="s">
+    <row r="52" spans="1:13">
+      <c r="A52" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F52" s="3" t="s">
+      <c r="D52" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G52" s="3">
-        <v>34</v>
-      </c>
-      <c r="H52" s="6">
+      <c r="G52" s="2">
+        <v>34</v>
+      </c>
+      <c r="H52" s="5">
         <v>832</v>
       </c>
-      <c r="I52" s="6">
+      <c r="I52" s="5">
         <v>138</v>
       </c>
-      <c r="J52" s="3">
-        <v>7</v>
-      </c>
-      <c r="K52" s="3" t="s">
+      <c r="J52" s="2">
+        <v>7</v>
+      </c>
+      <c r="K52" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="L52" s="6">
+      <c r="L52" s="5">
         <v>138</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:13" s="2" customFormat="1">
-      <c r="A53" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B53" s="3" t="s">
+    <row r="53" spans="1:13">
+      <c r="A53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F53" s="3" t="s">
+      <c r="D53" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G53" s="3">
-        <v>34</v>
-      </c>
-      <c r="H53" s="6">
+      <c r="G53" s="2">
+        <v>34</v>
+      </c>
+      <c r="H53" s="5">
         <v>2982</v>
       </c>
-      <c r="I53" s="6">
+      <c r="I53" s="5">
         <v>495</v>
       </c>
-      <c r="J53" s="3">
-        <v>7</v>
-      </c>
-      <c r="K53" s="3" t="s">
+      <c r="J53" s="2">
+        <v>7</v>
+      </c>
+      <c r="K53" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="L53" s="6">
+      <c r="L53" s="5">
         <v>495</v>
       </c>
-      <c r="M53" s="3">
+      <c r="M53" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:13" s="2" customFormat="1">
-      <c r="A54" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B54" s="3" t="s">
+    <row r="54" spans="1:13">
+      <c r="A54" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F54" s="3" t="s">
+      <c r="D54" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G54" s="3">
-        <v>34</v>
-      </c>
-      <c r="H54" s="6">
+      <c r="G54" s="2">
+        <v>34</v>
+      </c>
+      <c r="H54" s="5">
         <v>960</v>
       </c>
-      <c r="I54" s="6">
+      <c r="I54" s="5">
         <v>160</v>
       </c>
-      <c r="J54" s="3">
-        <v>7</v>
-      </c>
-      <c r="K54" s="3" t="s">
+      <c r="J54" s="2">
+        <v>7</v>
+      </c>
+      <c r="K54" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="L54" s="6">
+      <c r="L54" s="5">
         <v>160</v>
       </c>
-      <c r="M54" s="3">
+      <c r="M54" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:13">
-      <c r="L55">
-        <f>SUM(L2:L54)</f>
-        <v>35362</v>
-      </c>
-      <c r="M55" s="10">
-        <f>SUM(M2:M54)</f>
-        <v>1267</v>
-      </c>
+      <c r="M55" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2929,23 +2930,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M56"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -4813,7 +4814,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A4:N57">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:N57">
     <sortCondition ref="B1:B57"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/population.xlsx
+++ b/population.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b00e9cd42f584bf2/Documents/Population visualizer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{902D0A46-30B1-4E0E-BEEA-BF2A24C7BFC4}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85E29D68-1AC9-47F0-BBCE-C9B8E474A284}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="121">
   <si>
     <t>Region</t>
   </si>
@@ -395,6 +395,9 @@
   </si>
   <si>
     <t>Kokaya (ጎካያ)</t>
+  </si>
+  <si>
+    <t>Administrative Towns</t>
   </si>
 </sst>
 </file>
@@ -843,7 +846,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>42</v>
@@ -885,7 +888,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>42</v>
@@ -927,7 +930,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>43</v>
@@ -969,7 +972,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>43</v>

--- a/population.xlsx
+++ b/population.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b00e9cd42f584bf2/Documents/Population visualizer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85E29D68-1AC9-47F0-BBCE-C9B8E474A284}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75A5B825-2330-4024-BF50-9C50DB4364D4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2259,7 +2259,7 @@
         <v>7</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>101</v>
@@ -2284,7 +2284,7 @@
         <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>102</v>

--- a/population.xlsx
+++ b/population.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b00e9cd42f584bf2/Documents/Population visualizer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75A5B825-2330-4024-BF50-9C50DB4364D4}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7C57A2B-BEFD-410B-AFCB-17608D1C4BFB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="122">
   <si>
     <t>Region</t>
   </si>
@@ -398,6 +398,9 @@
   </si>
   <si>
     <t>Administrative Towns</t>
+  </si>
+  <si>
+    <t>Kamashi Town</t>
   </si>
 </sst>
 </file>
@@ -782,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
@@ -921,7 +924,7 @@
         <v>2305</v>
       </c>
       <c r="M3" s="2">
-        <f t="shared" ref="M3:M54" si="0">ROUND((SUM(1267*L3)/35362)+0.08,0)</f>
+        <f t="shared" ref="M3:M55" si="0">ROUND((SUM(1267*L3)/35362)+0.08,0)</f>
         <v>83</v>
       </c>
     </row>
@@ -2287,7 +2290,7 @@
         <v>120</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>34</v>
@@ -2320,157 +2323,157 @@
         <v>88</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G40" s="2">
+        <v>19</v>
+      </c>
+      <c r="H40" s="2">
+        <v>31271</v>
+      </c>
+      <c r="I40" s="2">
+        <v>5066</v>
+      </c>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G40" s="2">
+      <c r="D41" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G41" s="2">
         <v>15</v>
       </c>
-      <c r="H40" s="5">
+      <c r="H41" s="5">
         <v>950</v>
       </c>
-      <c r="I40" s="5">
+      <c r="I41" s="5">
         <v>153</v>
       </c>
-      <c r="J40" s="2">
+      <c r="J41" s="2">
         <v>3</v>
       </c>
-      <c r="K40" s="2" t="s">
+      <c r="K41" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="L40" s="5">
+      <c r="L41" s="5">
         <v>153</v>
       </c>
-      <c r="M40" s="2">
+      <c r="M41" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
-      <c r="A41" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" s="2" t="s">
+    <row r="42" spans="1:13">
+      <c r="A42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G41" s="2">
+      <c r="D42" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G42" s="2">
         <v>15</v>
       </c>
-      <c r="H41" s="5">
+      <c r="H42" s="5">
         <v>2624</v>
       </c>
-      <c r="I41" s="5">
+      <c r="I42" s="5">
         <v>425</v>
       </c>
-      <c r="J41" s="2">
+      <c r="J42" s="2">
         <v>3</v>
       </c>
-      <c r="K41" s="2" t="s">
+      <c r="K42" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="L41" s="5">
+      <c r="L42" s="5">
         <v>425</v>
       </c>
-      <c r="M41" s="2">
+      <c r="M42" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
-      <c r="A42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B42" s="2" t="s">
+    <row r="43" spans="1:13">
+      <c r="A43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G42" s="2">
+      <c r="D43" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G43" s="2">
         <v>15</v>
       </c>
-      <c r="H42" s="5">
+      <c r="H43" s="5">
         <v>1967</v>
       </c>
-      <c r="I42" s="5">
+      <c r="I43" s="5">
         <v>318</v>
       </c>
-      <c r="J42" s="2">
+      <c r="J43" s="2">
         <v>3</v>
       </c>
-      <c r="K42" s="2" t="s">
+      <c r="K43" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L42" s="5">
+      <c r="L43" s="5">
         <v>318</v>
       </c>
-      <c r="M42" s="2">
+      <c r="M43" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
-      <c r="A43" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G43" s="2">
-        <v>12</v>
-      </c>
-      <c r="H43" s="2">
-        <v>52709</v>
-      </c>
-      <c r="I43" s="2">
-        <v>8539</v>
-      </c>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
-    </row>
     <row r="44" spans="1:13">
       <c r="A44" s="2" t="s">
         <v>7</v>
@@ -2479,25 +2482,25 @@
         <v>88</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G44" s="2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H44" s="2">
-        <v>39823</v>
+        <v>52709</v>
       </c>
       <c r="I44" s="2">
-        <v>6451</v>
+        <v>8539</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -2512,420 +2515,453 @@
         <v>88</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G45" s="2">
+        <v>22</v>
+      </c>
+      <c r="H45" s="2">
+        <v>39823</v>
+      </c>
+      <c r="I45" s="2">
+        <v>6451</v>
+      </c>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G45" s="2">
+      <c r="D46" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G46" s="2">
         <v>15</v>
       </c>
-      <c r="H45" s="5">
+      <c r="H46" s="5">
         <v>1541</v>
       </c>
-      <c r="I45" s="5">
+      <c r="I46" s="5">
         <v>250</v>
       </c>
-      <c r="J45" s="2">
+      <c r="J46" s="2">
         <v>3</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="K46" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="L45" s="5">
+      <c r="L46" s="5">
         <v>250</v>
       </c>
-      <c r="M45" s="2">
+      <c r="M46" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
-      <c r="A46" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" s="2" t="s">
+    <row r="47" spans="1:13">
+      <c r="A47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G46" s="2">
+      <c r="D47" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G47" s="2">
         <v>15</v>
       </c>
-      <c r="H46" s="5">
+      <c r="H47" s="5">
         <v>872</v>
       </c>
-      <c r="I46" s="5">
+      <c r="I47" s="5">
         <v>141</v>
       </c>
-      <c r="J46" s="2">
+      <c r="J47" s="2">
         <v>3</v>
       </c>
-      <c r="K46" s="3" t="s">
+      <c r="K47" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="L46" s="5">
+      <c r="L47" s="5">
         <v>141</v>
       </c>
-      <c r="M46" s="2">
+      <c r="M47" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
-      <c r="A47" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B47" s="2" t="s">
+    <row r="48" spans="1:13">
+      <c r="A48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G47" s="2">
+      <c r="D48" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G48" s="2">
         <v>15</v>
       </c>
-      <c r="H47" s="5">
+      <c r="H48" s="5">
         <v>3487</v>
       </c>
-      <c r="I47" s="5">
+      <c r="I48" s="5">
         <v>565</v>
       </c>
-      <c r="J47" s="2">
+      <c r="J48" s="2">
         <v>3</v>
       </c>
-      <c r="K47" s="2" t="s">
+      <c r="K48" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="L47" s="5">
+      <c r="L48" s="5">
         <v>565</v>
       </c>
-      <c r="M47" s="2">
+      <c r="M48" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
-      <c r="A48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" s="2" t="s">
+    <row r="49" spans="1:13">
+      <c r="A49" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F48" s="2" t="s">
+      <c r="D49" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F49" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G48" s="2">
-        <v>34</v>
-      </c>
-      <c r="H48" s="5">
+      <c r="G49" s="2">
+        <v>34</v>
+      </c>
+      <c r="H49" s="5">
         <v>3933</v>
       </c>
-      <c r="I48" s="7">
+      <c r="I49" s="7">
         <v>654</v>
       </c>
-      <c r="J48" s="2">
-        <v>7</v>
-      </c>
-      <c r="K48" s="2" t="s">
+      <c r="J49" s="2">
+        <v>7</v>
+      </c>
+      <c r="K49" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="L48" s="7">
+      <c r="L49" s="7">
         <v>654</v>
       </c>
-      <c r="M48" s="2">
+      <c r="M49" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
-      <c r="A49" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B49" s="2" t="s">
+    <row r="50" spans="1:13">
+      <c r="A50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F49" s="2" t="s">
+      <c r="D50" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G49" s="2">
-        <v>34</v>
-      </c>
-      <c r="H49" s="5">
+      <c r="G50" s="2">
+        <v>34</v>
+      </c>
+      <c r="H50" s="5">
         <v>7519</v>
       </c>
-      <c r="I49" s="5">
+      <c r="I50" s="5">
         <v>1249</v>
       </c>
-      <c r="J49" s="2">
-        <v>7</v>
-      </c>
-      <c r="K49" s="2" t="s">
+      <c r="J50" s="2">
+        <v>7</v>
+      </c>
+      <c r="K50" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="L49" s="5">
+      <c r="L50" s="5">
         <v>1249</v>
       </c>
-      <c r="M49" s="2">
+      <c r="M50" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
-      <c r="A50" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B50" s="2" t="s">
+    <row r="51" spans="1:13">
+      <c r="A51" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F50" s="2" t="s">
+      <c r="D51" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G50" s="2">
-        <v>34</v>
-      </c>
-      <c r="H50" s="5">
+      <c r="G51" s="2">
+        <v>34</v>
+      </c>
+      <c r="H51" s="5">
         <v>4245</v>
       </c>
-      <c r="I50" s="5">
+      <c r="I51" s="5">
         <v>705</v>
       </c>
-      <c r="J50" s="2">
-        <v>7</v>
-      </c>
-      <c r="K50" s="2" t="s">
+      <c r="J51" s="2">
+        <v>7</v>
+      </c>
+      <c r="K51" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="L50" s="5">
+      <c r="L51" s="5">
         <v>705</v>
       </c>
-      <c r="M50" s="2">
+      <c r="M51" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
-      <c r="A51" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B51" s="2" t="s">
+    <row r="52" spans="1:13">
+      <c r="A52" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F51" s="2" t="s">
+      <c r="D52" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G51" s="2">
-        <v>34</v>
-      </c>
-      <c r="H51" s="5">
+      <c r="G52" s="2">
+        <v>34</v>
+      </c>
+      <c r="H52" s="5">
         <v>736</v>
       </c>
-      <c r="I51" s="5">
+      <c r="I52" s="5">
         <v>122</v>
       </c>
-      <c r="J51" s="2">
-        <v>7</v>
-      </c>
-      <c r="K51" s="2" t="s">
+      <c r="J52" s="2">
+        <v>7</v>
+      </c>
+      <c r="K52" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L51" s="5">
+      <c r="L52" s="5">
         <v>122</v>
       </c>
-      <c r="M51" s="2">
+      <c r="M52" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
-      <c r="A52" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B52" s="2" t="s">
+    <row r="53" spans="1:13">
+      <c r="A53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F52" s="2" t="s">
+      <c r="D53" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G52" s="2">
-        <v>34</v>
-      </c>
-      <c r="H52" s="5">
+      <c r="G53" s="2">
+        <v>34</v>
+      </c>
+      <c r="H53" s="5">
         <v>832</v>
       </c>
-      <c r="I52" s="5">
+      <c r="I53" s="5">
         <v>138</v>
       </c>
-      <c r="J52" s="2">
-        <v>7</v>
-      </c>
-      <c r="K52" s="2" t="s">
+      <c r="J53" s="2">
+        <v>7</v>
+      </c>
+      <c r="K53" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="L52" s="5">
+      <c r="L53" s="5">
         <v>138</v>
       </c>
-      <c r="M52" s="2">
+      <c r="M53" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
-      <c r="A53" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B53" s="2" t="s">
+    <row r="54" spans="1:13">
+      <c r="A54" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F53" s="2" t="s">
+      <c r="D54" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G53" s="2">
-        <v>34</v>
-      </c>
-      <c r="H53" s="5">
+      <c r="G54" s="2">
+        <v>34</v>
+      </c>
+      <c r="H54" s="5">
         <v>2982</v>
       </c>
-      <c r="I53" s="5">
+      <c r="I54" s="5">
         <v>495</v>
       </c>
-      <c r="J53" s="2">
-        <v>7</v>
-      </c>
-      <c r="K53" s="2" t="s">
+      <c r="J54" s="2">
+        <v>7</v>
+      </c>
+      <c r="K54" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="L53" s="5">
+      <c r="L54" s="5">
         <v>495</v>
       </c>
-      <c r="M53" s="2">
+      <c r="M54" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
-      <c r="A54" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B54" s="2" t="s">
+    <row r="55" spans="1:13">
+      <c r="A55" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F54" s="2" t="s">
+      <c r="D55" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G54" s="2">
-        <v>34</v>
-      </c>
-      <c r="H54" s="5">
+      <c r="G55" s="2">
+        <v>34</v>
+      </c>
+      <c r="H55" s="5">
         <v>960</v>
       </c>
-      <c r="I54" s="5">
+      <c r="I55" s="5">
         <v>160</v>
       </c>
-      <c r="J54" s="2">
-        <v>7</v>
-      </c>
-      <c r="K54" s="2" t="s">
+      <c r="J55" s="2">
+        <v>7</v>
+      </c>
+      <c r="K55" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="L54" s="5">
+      <c r="L55" s="5">
         <v>160</v>
       </c>
-      <c r="M54" s="2">
+      <c r="M55" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
-      <c r="M55" s="8"/>
+    <row r="56" spans="1:13">
+      <c r="M56" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/population.xlsx
+++ b/population.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b00e9cd42f584bf2/Documents/Population visualizer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7C57A2B-BEFD-410B-AFCB-17608D1C4BFB}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3785D29F-7C2B-4ED2-BEC3-A032665FE8E6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -407,7 +407,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,6 +434,10 @@
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="ተቲመ"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="ተቲመ"/>
     </font>
   </fonts>
@@ -489,7 +493,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -505,6 +509,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1013,31 +1018,31 @@
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="D6" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="9">
         <v>44</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="9">
         <v>85148</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="9">
         <v>13794</v>
       </c>
       <c r="J6" s="4"/>

--- a/population.xlsx
+++ b/population.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b00e9cd42f584bf2/Documents/Population visualizer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3785D29F-7C2B-4ED2-BEC3-A032665FE8E6}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{833D2782-CCD0-4A5A-B267-BA78EC6A9A04}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="124">
   <si>
     <t>Region</t>
   </si>
@@ -401,6 +401,12 @@
   </si>
   <si>
     <t>Kamashi Town</t>
+  </si>
+  <si>
+    <t>Non Mining</t>
+  </si>
+  <si>
+    <t>Mining Status</t>
   </si>
 </sst>
 </file>
@@ -819,7 +825,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>36</v>
@@ -860,7 +866,7 @@
         <v>42</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>40</v>
@@ -902,7 +908,7 @@
         <v>42</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>40</v>
@@ -944,7 +950,7 @@
         <v>43</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>40</v>
@@ -986,7 +992,7 @@
         <v>43</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>40</v>
@@ -1027,8 +1033,8 @@
       <c r="C6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>39</v>
+      <c r="D6" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>40</v>
@@ -1061,7 +1067,7 @@
         <v>110</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>40</v>
@@ -1103,7 +1109,7 @@
         <v>110</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>40</v>
@@ -1145,7 +1151,7 @@
         <v>110</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>40</v>
@@ -1187,7 +1193,7 @@
         <v>110</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>40</v>
@@ -1229,7 +1235,7 @@
         <v>110</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>40</v>
@@ -1271,7 +1277,7 @@
         <v>110</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>40</v>
@@ -1313,7 +1319,7 @@
         <v>25</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>40</v>
@@ -1346,7 +1352,7 @@
         <v>23</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>40</v>
@@ -1379,7 +1385,7 @@
         <v>89</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>40</v>
@@ -1646,7 +1652,7 @@
         <v>93</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>36</v>
@@ -1688,7 +1694,7 @@
         <v>93</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>36</v>
@@ -1730,7 +1736,7 @@
         <v>93</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>36</v>
@@ -1805,7 +1811,7 @@
         <v>95</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>40</v>
@@ -1847,7 +1853,7 @@
         <v>95</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>40</v>
@@ -1889,7 +1895,7 @@
         <v>95</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>40</v>
@@ -1931,7 +1937,7 @@
         <v>95</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>40</v>
@@ -2006,7 +2012,7 @@
         <v>97</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>36</v>
@@ -2039,7 +2045,7 @@
         <v>98</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>36</v>
@@ -2273,7 +2279,7 @@
         <v>101</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>40</v>
@@ -2682,7 +2688,7 @@
         <v>33</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>36</v>
@@ -2724,7 +2730,7 @@
         <v>33</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>36</v>
@@ -2766,7 +2772,7 @@
         <v>33</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>36</v>
@@ -2808,7 +2814,7 @@
         <v>33</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>36</v>
@@ -2850,7 +2856,7 @@
         <v>33</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>36</v>
@@ -2892,7 +2898,7 @@
         <v>33</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>36</v>
@@ -2934,7 +2940,7 @@
         <v>33</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>36</v>

--- a/population.xlsx
+++ b/population.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b00e9cd42f584bf2/Documents/Population visualizer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{833D2782-CCD0-4A5A-B267-BA78EC6A9A04}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F8D1C5C-BCB1-4B10-B60F-8915E269A51B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="123">
   <si>
     <t>Region</t>
   </si>
@@ -404,9 +404,6 @@
   </si>
   <si>
     <t>Non Mining</t>
-  </si>
-  <si>
-    <t>Mining Status</t>
   </si>
 </sst>
 </file>
@@ -825,7 +822,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>123</v>
+        <v>34</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>36</v>

--- a/population.xlsx
+++ b/population.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b00e9cd42f584bf2/Documents/Population visualizer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F8D1C5C-BCB1-4B10-B60F-8915E269A51B}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B95F95D-042D-4D18-A12D-F1C24E5FD083}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -962,7 +962,7 @@
         <v>2005</v>
       </c>
       <c r="I4" s="3">
-        <v>1460</v>
+        <v>324</v>
       </c>
       <c r="J4" s="2">
         <v>2</v>
@@ -1004,7 +1004,7 @@
         <v>2274</v>
       </c>
       <c r="I5" s="3">
-        <v>1656</v>
+        <v>368</v>
       </c>
       <c r="J5" s="2">
         <v>2</v>
@@ -2969,6 +2969,10 @@
       </c>
     </row>
     <row r="56" spans="1:13">
+      <c r="L56">
+        <f>SUM(L2:L55)</f>
+        <v>35362</v>
+      </c>
       <c r="M56" s="8"/>
     </row>
   </sheetData>

--- a/population.xlsx
+++ b/population.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b00e9cd42f584bf2/Documents/Population visualizer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B95F95D-042D-4D18-A12D-F1C24E5FD083}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DC76145-D803-4EF5-AF0B-9587212BD112}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="124">
   <si>
     <t>Region</t>
   </si>
@@ -404,6 +404,9 @@
   </si>
   <si>
     <t>Non Mining</t>
+  </si>
+  <si>
+    <t>Get Seya (ግት ስያ)</t>
   </si>
 </sst>
 </file>
@@ -793,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
@@ -804,14 +807,13 @@
     <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
     <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.109375" customWidth="1"/>
-    <col min="11" max="11" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.109375" customWidth="1"/>
+    <col min="10" max="10" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -837,22 +839,19 @@
         <v>3</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M1" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -877,24 +876,21 @@
       <c r="H2" s="3">
         <v>7118</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="2">
+        <v>2</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K2" s="3">
         <v>1151</v>
       </c>
-      <c r="J2" s="2">
-        <v>2</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L2" s="3">
-        <v>1151</v>
-      </c>
-      <c r="M2" s="2">
-        <f>ROUND((SUM(1267*L2)/35362)+0.08,0)</f>
+      <c r="L2" s="2">
+        <f>ROUND((SUM(1267*K2)/35362)+0.08,0)</f>
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -919,24 +915,21 @@
       <c r="H3" s="3">
         <v>14250</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
+        <v>2</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="3">
         <v>2305</v>
       </c>
-      <c r="J3" s="2">
-        <v>2</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L3" s="3">
-        <v>2305</v>
-      </c>
-      <c r="M3" s="2">
-        <f t="shared" ref="M3:M55" si="0">ROUND((SUM(1267*L3)/35362)+0.08,0)</f>
+      <c r="L3" s="2">
+        <f t="shared" ref="L3:L55" si="0">ROUND((SUM(1267*K3)/35362)+0.08,0)</f>
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -961,24 +954,21 @@
       <c r="H4" s="3">
         <v>2005</v>
       </c>
-      <c r="I4" s="3">
-        <v>324</v>
-      </c>
-      <c r="J4" s="2">
+      <c r="I4" s="2">
         <v>2</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="L4" s="3">
+      <c r="K4" s="3">
         <v>1460</v>
       </c>
-      <c r="M4" s="2">
+      <c r="L4" s="2">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -1003,24 +993,21 @@
       <c r="H5" s="3">
         <v>2274</v>
       </c>
-      <c r="I5" s="3">
-        <v>368</v>
-      </c>
-      <c r="J5" s="2">
+      <c r="I5" s="2">
         <v>2</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L5" s="3">
+      <c r="K5" s="3">
         <v>1656</v>
       </c>
-      <c r="M5" s="2">
+      <c r="L5" s="2">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:12">
       <c r="A6" s="9" t="s">
         <v>7</v>
       </c>
@@ -1045,15 +1032,12 @@
       <c r="H6" s="9">
         <v>85148</v>
       </c>
-      <c r="I6" s="9">
-        <v>13794</v>
-      </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="I6" s="4"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1078,24 +1062,21 @@
       <c r="H7" s="5">
         <v>2226</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="2">
+        <v>6</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="K7" s="5">
         <v>361</v>
       </c>
-      <c r="J7" s="2">
-        <v>6</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="L7" s="5">
-        <v>361</v>
-      </c>
-      <c r="M7" s="2">
+      <c r="L7" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1120,24 +1101,21 @@
       <c r="H8" s="5">
         <v>2903</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="2">
+        <v>6</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="K8" s="5">
         <v>470</v>
       </c>
-      <c r="J8" s="2">
-        <v>6</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="L8" s="5">
-        <v>470</v>
-      </c>
-      <c r="M8" s="2">
+      <c r="L8" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -1162,24 +1140,21 @@
       <c r="H9" s="5">
         <v>1280</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="2">
+        <v>6</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="K9" s="5">
         <v>207</v>
       </c>
-      <c r="J9" s="2">
-        <v>6</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="L9" s="5">
-        <v>207</v>
-      </c>
-      <c r="M9" s="2">
+      <c r="L9" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -1204,24 +1179,21 @@
       <c r="H10" s="5">
         <v>4841</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="2">
+        <v>6</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K10" s="5">
         <v>784</v>
       </c>
-      <c r="J10" s="2">
-        <v>6</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="L10" s="5">
-        <v>784</v>
-      </c>
-      <c r="M10" s="2">
+      <c r="L10" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
@@ -1246,24 +1218,21 @@
       <c r="H11" s="5">
         <v>5400</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="2">
+        <v>6</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="K11" s="5">
         <v>874</v>
       </c>
-      <c r="J11" s="2">
-        <v>6</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="L11" s="5">
-        <v>874</v>
-      </c>
-      <c r="M11" s="2">
+      <c r="L11" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -1288,24 +1257,21 @@
       <c r="H12" s="5">
         <v>4371</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="2">
+        <v>6</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K12" s="5">
         <v>708</v>
       </c>
-      <c r="J12" s="2">
-        <v>6</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="L12" s="5">
-        <v>708</v>
-      </c>
-      <c r="M12" s="2">
+      <c r="L12" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1330,15 +1296,12 @@
       <c r="H13" s="2">
         <v>55983</v>
       </c>
-      <c r="I13" s="2">
-        <v>9069</v>
-      </c>
+      <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" spans="1:13">
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
@@ -1363,15 +1326,12 @@
       <c r="H14" s="2">
         <v>73845</v>
       </c>
-      <c r="I14" s="2">
-        <v>11963</v>
-      </c>
+      <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-    </row>
-    <row r="15" spans="1:13">
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -1396,15 +1356,12 @@
       <c r="H15" s="2">
         <v>38021</v>
       </c>
-      <c r="I15" s="2">
-        <v>6159</v>
-      </c>
+      <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-    </row>
-    <row r="16" spans="1:13">
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
@@ -1429,15 +1386,12 @@
       <c r="H16" s="2">
         <v>45722</v>
       </c>
-      <c r="I16" s="2">
-        <v>7407</v>
-      </c>
+      <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" spans="1:13">
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
@@ -1462,15 +1416,12 @@
       <c r="H17" s="2">
         <v>43153</v>
       </c>
-      <c r="I17" s="2">
-        <v>6991</v>
-      </c>
+      <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="1:13">
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
@@ -1495,24 +1446,21 @@
       <c r="H18" s="5">
         <v>1545</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="2">
+        <v>4</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K18" s="5">
         <v>250</v>
       </c>
-      <c r="J18" s="2">
-        <v>4</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="L18" s="5">
-        <v>250</v>
-      </c>
-      <c r="M18" s="2">
+      <c r="L18" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:12">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -1537,24 +1485,21 @@
       <c r="H19" s="5">
         <v>2057</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="2">
+        <v>4</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K19" s="5">
         <v>333</v>
       </c>
-      <c r="J19" s="2">
-        <v>4</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L19" s="5">
-        <v>333</v>
-      </c>
-      <c r="M19" s="2">
+      <c r="L19" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:12">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -1579,24 +1524,21 @@
       <c r="H20" s="5">
         <v>1727</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="2">
+        <v>4</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K20" s="5">
         <v>278</v>
       </c>
-      <c r="J20" s="2">
-        <v>4</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L20" s="5">
-        <v>278</v>
-      </c>
-      <c r="M20" s="2">
+      <c r="L20" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:12">
       <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
@@ -1621,24 +1563,21 @@
       <c r="H21" s="5">
         <v>1867</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="2">
+        <v>4</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K21" s="5">
         <v>302</v>
       </c>
-      <c r="J21" s="2">
-        <v>4</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L21" s="5">
-        <v>302</v>
-      </c>
-      <c r="M21" s="2">
+      <c r="L21" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:12">
       <c r="A22" s="2" t="s">
         <v>7</v>
       </c>
@@ -1663,24 +1602,21 @@
       <c r="H22" s="5">
         <v>1858</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="2">
+        <v>3</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K22" s="5">
         <v>301</v>
       </c>
-      <c r="J22" s="2">
-        <v>3</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L22" s="5">
-        <v>301</v>
-      </c>
-      <c r="M22" s="2">
+      <c r="L22" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:12">
       <c r="A23" s="2" t="s">
         <v>7</v>
       </c>
@@ -1705,24 +1641,21 @@
       <c r="H23" s="5">
         <v>2184</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="2">
+        <v>3</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K23" s="5">
         <v>353</v>
       </c>
-      <c r="J23" s="2">
-        <v>3</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="L23" s="5">
-        <v>353</v>
-      </c>
-      <c r="M23" s="2">
+      <c r="L23" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:12">
       <c r="A24" s="2" t="s">
         <v>7</v>
       </c>
@@ -1747,24 +1680,21 @@
       <c r="H24" s="5">
         <v>4167</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I24" s="2">
+        <v>3</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K24" s="5">
         <v>674</v>
       </c>
-      <c r="J24" s="2">
-        <v>3</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="L24" s="5">
-        <v>674</v>
-      </c>
-      <c r="M24" s="2">
+      <c r="L24" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:12">
       <c r="A25" s="2" t="s">
         <v>7</v>
       </c>
@@ -1789,15 +1719,12 @@
       <c r="H25" s="2">
         <v>71256</v>
       </c>
-      <c r="I25" s="2">
-        <v>11543</v>
-      </c>
+      <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-    </row>
-    <row r="26" spans="1:13">
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="2" t="s">
         <v>7</v>
       </c>
@@ -1822,24 +1749,21 @@
       <c r="H26" s="6">
         <v>5938</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="2">
+        <v>4</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K26" s="5">
         <v>962</v>
       </c>
-      <c r="J26" s="2">
-        <v>4</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="L26" s="5">
-        <v>962</v>
-      </c>
-      <c r="M26" s="2">
+      <c r="L26" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:12">
       <c r="A27" s="2" t="s">
         <v>7</v>
       </c>
@@ -1864,24 +1788,21 @@
       <c r="H27" s="6">
         <v>3340</v>
       </c>
-      <c r="I27" s="5">
+      <c r="I27" s="2">
+        <v>4</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K27" s="5">
         <v>541</v>
       </c>
-      <c r="J27" s="2">
-        <v>4</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="L27" s="5">
-        <v>541</v>
-      </c>
-      <c r="M27" s="2">
+      <c r="L27" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:12">
       <c r="A28" s="2" t="s">
         <v>7</v>
       </c>
@@ -1907,23 +1828,20 @@
         <v>79654</v>
       </c>
       <c r="I28" s="2">
+        <v>4</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K28" s="2">
         <v>12904</v>
       </c>
-      <c r="J28" s="2">
-        <v>4</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="L28" s="2">
-        <v>12904</v>
-      </c>
-      <c r="M28" s="2">
         <f t="shared" si="0"/>
         <v>462</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:12">
       <c r="A29" s="2" t="s">
         <v>7</v>
       </c>
@@ -1948,24 +1866,21 @@
       <c r="H29" s="5">
         <v>2339</v>
       </c>
-      <c r="I29" s="5">
+      <c r="I29" s="2">
+        <v>4</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K29" s="5">
         <v>379</v>
       </c>
-      <c r="J29" s="2">
-        <v>4</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="L29" s="5">
-        <v>379</v>
-      </c>
-      <c r="M29" s="2">
+      <c r="L29" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:12">
       <c r="A30" s="2" t="s">
         <v>7</v>
       </c>
@@ -1990,15 +1905,12 @@
       <c r="H30" s="2">
         <v>84872</v>
       </c>
-      <c r="I30" s="2">
-        <v>13749</v>
-      </c>
+      <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-    </row>
-    <row r="31" spans="1:13">
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" s="2" t="s">
         <v>7</v>
       </c>
@@ -2023,15 +1935,12 @@
       <c r="H31" s="2">
         <v>26067</v>
       </c>
-      <c r="I31" s="2">
-        <v>4223</v>
-      </c>
+      <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-    </row>
-    <row r="32" spans="1:13">
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="2" t="s">
         <v>7</v>
       </c>
@@ -2056,15 +1965,12 @@
       <c r="H32" s="2">
         <v>77639</v>
       </c>
-      <c r="I32" s="2">
-        <v>12577</v>
-      </c>
+      <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-    </row>
-    <row r="33" spans="1:13">
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33" s="2" t="s">
         <v>7</v>
       </c>
@@ -2089,24 +1995,21 @@
       <c r="H33" s="5">
         <v>6610</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I33" s="2">
+        <v>4</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K33" s="5">
         <v>1069</v>
       </c>
-      <c r="J33" s="2">
-        <v>4</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="L33" s="5">
-        <v>1069</v>
-      </c>
-      <c r="M33" s="2">
+      <c r="L33" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:12">
       <c r="A34" s="2" t="s">
         <v>7</v>
       </c>
@@ -2131,24 +2034,21 @@
       <c r="H34" s="5">
         <v>2878</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I34" s="2">
+        <v>4</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K34" s="5">
         <v>466</v>
       </c>
-      <c r="J34" s="2">
-        <v>4</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="L34" s="5">
-        <v>466</v>
-      </c>
-      <c r="M34" s="2">
+      <c r="L34" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:12">
       <c r="A35" s="2" t="s">
         <v>7</v>
       </c>
@@ -2173,24 +2073,21 @@
       <c r="H35" s="5">
         <v>3758</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I35" s="2">
+        <v>4</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="5">
         <v>608</v>
       </c>
-      <c r="J35" s="2">
-        <v>4</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L35" s="5">
-        <v>608</v>
-      </c>
-      <c r="M35" s="2">
+      <c r="L35" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:12">
       <c r="A36" s="2" t="s">
         <v>7</v>
       </c>
@@ -2215,24 +2112,21 @@
       <c r="H36" s="5">
         <v>3658</v>
       </c>
-      <c r="I36" s="5">
+      <c r="I36" s="2">
+        <v>4</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K36" s="5">
         <v>591</v>
       </c>
-      <c r="J36" s="2">
-        <v>4</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L36" s="5">
-        <v>591</v>
-      </c>
-      <c r="M36" s="2">
+      <c r="L36" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:12">
       <c r="A37" s="2" t="s">
         <v>7</v>
       </c>
@@ -2257,15 +2151,12 @@
       <c r="H37" s="2">
         <v>104918</v>
       </c>
-      <c r="I37" s="2">
-        <v>16997</v>
-      </c>
+      <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-    </row>
-    <row r="38" spans="1:13">
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38" s="2" t="s">
         <v>7</v>
       </c>
@@ -2288,9 +2179,8 @@
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="1:13">
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39" s="2" t="s">
         <v>7</v>
       </c>
@@ -2315,15 +2205,12 @@
       <c r="H39" s="2">
         <v>31271</v>
       </c>
-      <c r="I39" s="2">
-        <v>5066</v>
-      </c>
+      <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-    </row>
-    <row r="40" spans="1:13">
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40" s="2" t="s">
         <v>7</v>
       </c>
@@ -2348,15 +2235,12 @@
       <c r="H40" s="2">
         <v>31271</v>
       </c>
-      <c r="I40" s="2">
-        <v>5066</v>
-      </c>
+      <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
-    </row>
-    <row r="41" spans="1:13">
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" s="2" t="s">
         <v>7</v>
       </c>
@@ -2381,24 +2265,21 @@
       <c r="H41" s="5">
         <v>950</v>
       </c>
-      <c r="I41" s="5">
+      <c r="I41" s="2">
+        <v>3</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K41" s="5">
         <v>153</v>
       </c>
-      <c r="J41" s="2">
-        <v>3</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L41" s="5">
-        <v>153</v>
-      </c>
-      <c r="M41" s="2">
+      <c r="L41" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:12">
       <c r="A42" s="2" t="s">
         <v>7</v>
       </c>
@@ -2423,24 +2304,21 @@
       <c r="H42" s="5">
         <v>2624</v>
       </c>
-      <c r="I42" s="5">
+      <c r="I42" s="2">
+        <v>3</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K42" s="5">
         <v>425</v>
       </c>
-      <c r="J42" s="2">
-        <v>3</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="L42" s="5">
-        <v>425</v>
-      </c>
-      <c r="M42" s="2">
+      <c r="L42" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:12">
       <c r="A43" s="2" t="s">
         <v>7</v>
       </c>
@@ -2465,24 +2343,21 @@
       <c r="H43" s="5">
         <v>1967</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I43" s="2">
+        <v>3</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K43" s="5">
         <v>318</v>
       </c>
-      <c r="J43" s="2">
-        <v>3</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L43" s="5">
-        <v>318</v>
-      </c>
-      <c r="M43" s="2">
+      <c r="L43" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:12">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
@@ -2507,15 +2382,12 @@
       <c r="H44" s="2">
         <v>52709</v>
       </c>
-      <c r="I44" s="2">
-        <v>8539</v>
-      </c>
+      <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
-    </row>
-    <row r="45" spans="1:13">
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45" s="2" t="s">
         <v>7</v>
       </c>
@@ -2540,15 +2412,12 @@
       <c r="H45" s="2">
         <v>39823</v>
       </c>
-      <c r="I45" s="2">
-        <v>6451</v>
-      </c>
+      <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-    </row>
-    <row r="46" spans="1:13">
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46" s="2" t="s">
         <v>7</v>
       </c>
@@ -2573,24 +2442,21 @@
       <c r="H46" s="5">
         <v>1541</v>
       </c>
-      <c r="I46" s="5">
+      <c r="I46" s="2">
+        <v>3</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="K46" s="5">
         <v>250</v>
       </c>
-      <c r="J46" s="2">
-        <v>3</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="L46" s="5">
-        <v>250</v>
-      </c>
-      <c r="M46" s="2">
+      <c r="L46" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:12">
       <c r="A47" s="2" t="s">
         <v>7</v>
       </c>
@@ -2615,24 +2481,21 @@
       <c r="H47" s="5">
         <v>872</v>
       </c>
-      <c r="I47" s="5">
+      <c r="I47" s="2">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K47" s="5">
         <v>141</v>
       </c>
-      <c r="J47" s="2">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="L47" s="5">
-        <v>141</v>
-      </c>
-      <c r="M47" s="2">
+      <c r="L47" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:12">
       <c r="A48" s="2" t="s">
         <v>7</v>
       </c>
@@ -2657,24 +2520,21 @@
       <c r="H48" s="5">
         <v>3487</v>
       </c>
-      <c r="I48" s="5">
+      <c r="I48" s="2">
+        <v>3</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K48" s="5">
         <v>565</v>
       </c>
-      <c r="J48" s="2">
-        <v>3</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L48" s="5">
-        <v>565</v>
-      </c>
-      <c r="M48" s="2">
+      <c r="L48" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:12">
       <c r="A49" s="2" t="s">
         <v>7</v>
       </c>
@@ -2699,24 +2559,21 @@
       <c r="H49" s="5">
         <v>3933</v>
       </c>
-      <c r="I49" s="7">
+      <c r="I49" s="2">
+        <v>7</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K49" s="7">
         <v>654</v>
       </c>
-      <c r="J49" s="2">
-        <v>7</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L49" s="7">
-        <v>654</v>
-      </c>
-      <c r="M49" s="2">
+      <c r="L49" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:12">
       <c r="A50" s="2" t="s">
         <v>7</v>
       </c>
@@ -2741,24 +2598,21 @@
       <c r="H50" s="5">
         <v>7519</v>
       </c>
-      <c r="I50" s="5">
+      <c r="I50" s="2">
+        <v>7</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K50" s="5">
         <v>1249</v>
       </c>
-      <c r="J50" s="2">
-        <v>7</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L50" s="5">
-        <v>1249</v>
-      </c>
-      <c r="M50" s="2">
+      <c r="L50" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:12">
       <c r="A51" s="2" t="s">
         <v>7</v>
       </c>
@@ -2783,24 +2637,21 @@
       <c r="H51" s="5">
         <v>4245</v>
       </c>
-      <c r="I51" s="5">
+      <c r="I51" s="2">
+        <v>7</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K51" s="5">
         <v>705</v>
       </c>
-      <c r="J51" s="2">
-        <v>7</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L51" s="5">
-        <v>705</v>
-      </c>
-      <c r="M51" s="2">
+      <c r="L51" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:12">
       <c r="A52" s="2" t="s">
         <v>7</v>
       </c>
@@ -2825,24 +2676,21 @@
       <c r="H52" s="5">
         <v>736</v>
       </c>
-      <c r="I52" s="5">
+      <c r="I52" s="2">
+        <v>7</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K52" s="5">
         <v>122</v>
       </c>
-      <c r="J52" s="2">
-        <v>7</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L52" s="5">
-        <v>122</v>
-      </c>
-      <c r="M52" s="2">
+      <c r="L52" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:12">
       <c r="A53" s="2" t="s">
         <v>7</v>
       </c>
@@ -2867,24 +2715,21 @@
       <c r="H53" s="5">
         <v>832</v>
       </c>
-      <c r="I53" s="5">
+      <c r="I53" s="2">
+        <v>7</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K53" s="5">
         <v>138</v>
       </c>
-      <c r="J53" s="2">
-        <v>7</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L53" s="5">
-        <v>138</v>
-      </c>
-      <c r="M53" s="2">
+      <c r="L53" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:12">
       <c r="A54" s="2" t="s">
         <v>7</v>
       </c>
@@ -2909,24 +2754,21 @@
       <c r="H54" s="5">
         <v>2982</v>
       </c>
-      <c r="I54" s="5">
+      <c r="I54" s="2">
+        <v>7</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K54" s="5">
         <v>495</v>
       </c>
-      <c r="J54" s="2">
-        <v>7</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="L54" s="5">
-        <v>495</v>
-      </c>
-      <c r="M54" s="2">
+      <c r="L54" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:12">
       <c r="A55" s="2" t="s">
         <v>7</v>
       </c>
@@ -2951,29 +2793,22 @@
       <c r="H55" s="5">
         <v>960</v>
       </c>
-      <c r="I55" s="5">
+      <c r="I55" s="2">
+        <v>7</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K55" s="5">
         <v>160</v>
       </c>
-      <c r="J55" s="2">
-        <v>7</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L55" s="5">
-        <v>160</v>
-      </c>
-      <c r="M55" s="2">
+      <c r="L55" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:13">
-      <c r="L56">
-        <f>SUM(L2:L55)</f>
-        <v>35362</v>
-      </c>
-      <c r="M56" s="8"/>
+    <row r="56" spans="1:12">
+      <c r="L56" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/population.xlsx
+++ b/population.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b00e9cd42f584bf2/Documents/Population visualizer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DC76145-D803-4EF5-AF0B-9587212BD112}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8C3DDF4-0BCF-481A-B792-0BFDE3217C84}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="124">
   <si>
     <t>Region</t>
   </si>
@@ -796,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
@@ -807,13 +807,14 @@
     <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
     <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.109375" customWidth="1"/>
-    <col min="10" max="10" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.109375" customWidth="1"/>
+    <col min="11" max="11" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -839,19 +840,22 @@
         <v>3</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -876,21 +880,24 @@
       <c r="H2" s="3">
         <v>7118</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="3">
+        <v>1151</v>
+      </c>
+      <c r="J2" s="2">
         <v>2</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="3">
+      <c r="L2" s="3">
         <v>1151</v>
       </c>
-      <c r="L2" s="2">
-        <f>ROUND((SUM(1267*K2)/35362)+0.08,0)</f>
+      <c r="M2" s="2">
+        <f>ROUND((SUM(1267*L2)/35362)+0.08,0)</f>
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -915,21 +922,24 @@
       <c r="H3" s="3">
         <v>14250</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="3">
+        <v>2305</v>
+      </c>
+      <c r="J3" s="2">
         <v>2</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="3">
+      <c r="L3" s="3">
         <v>2305</v>
       </c>
-      <c r="L3" s="2">
-        <f t="shared" ref="L3:L55" si="0">ROUND((SUM(1267*K3)/35362)+0.08,0)</f>
+      <c r="M3" s="2">
+        <f t="shared" ref="M3:M55" si="0">ROUND((SUM(1267*L3)/35362)+0.08,0)</f>
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -954,21 +964,24 @@
       <c r="H4" s="3">
         <v>2005</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="3">
+        <v>324</v>
+      </c>
+      <c r="J4" s="2">
         <v>2</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="K4" s="3">
-        <v>1460</v>
-      </c>
-      <c r="L4" s="2">
+      <c r="L4" s="3">
+        <v>324</v>
+      </c>
+      <c r="M4" s="2">
         <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -993,21 +1006,24 @@
       <c r="H5" s="3">
         <v>2274</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="3">
+        <v>368</v>
+      </c>
+      <c r="J5" s="2">
         <v>2</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="3">
-        <v>1656</v>
-      </c>
-      <c r="L5" s="2">
+      <c r="L5" s="3">
+        <v>368</v>
+      </c>
+      <c r="M5" s="2">
         <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="9" t="s">
         <v>7</v>
       </c>
@@ -1032,12 +1048,15 @@
       <c r="H6" s="9">
         <v>85148</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="2"/>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="I6" s="9">
+        <v>13794</v>
+      </c>
+      <c r="J6" s="4"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1062,21 +1081,24 @@
       <c r="H7" s="5">
         <v>2226</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="5">
+        <v>361</v>
+      </c>
+      <c r="J7" s="2">
         <v>6</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="K7" s="5">
+      <c r="L7" s="5">
         <v>361</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1101,21 +1123,24 @@
       <c r="H8" s="5">
         <v>2903</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="5">
+        <v>470</v>
+      </c>
+      <c r="J8" s="2">
         <v>6</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="K8" s="5">
+      <c r="L8" s="5">
         <v>470</v>
       </c>
-      <c r="L8" s="2">
+      <c r="M8" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -1140,21 +1165,24 @@
       <c r="H9" s="5">
         <v>1280</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="5">
+        <v>207</v>
+      </c>
+      <c r="J9" s="2">
         <v>6</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="K9" s="5">
+      <c r="L9" s="5">
         <v>207</v>
       </c>
-      <c r="L9" s="2">
+      <c r="M9" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:13">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -1179,21 +1207,24 @@
       <c r="H10" s="5">
         <v>4841</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="5">
+        <v>784</v>
+      </c>
+      <c r="J10" s="2">
         <v>6</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="K10" s="5">
+      <c r="L10" s="5">
         <v>784</v>
       </c>
-      <c r="L10" s="2">
+      <c r="M10" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:13">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
@@ -1218,21 +1249,24 @@
       <c r="H11" s="5">
         <v>5400</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="5">
+        <v>874</v>
+      </c>
+      <c r="J11" s="2">
         <v>6</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="K11" s="5">
+      <c r="L11" s="5">
         <v>874</v>
       </c>
-      <c r="L11" s="2">
+      <c r="M11" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:13">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -1257,21 +1291,24 @@
       <c r="H12" s="5">
         <v>4371</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="5">
+        <v>708</v>
+      </c>
+      <c r="J12" s="2">
         <v>6</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="K12" s="5">
+      <c r="L12" s="5">
         <v>708</v>
       </c>
-      <c r="L12" s="2">
+      <c r="M12" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:13">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1296,12 +1333,15 @@
       <c r="H13" s="2">
         <v>55983</v>
       </c>
-      <c r="I13" s="2"/>
+      <c r="I13" s="2">
+        <v>9069</v>
+      </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
@@ -1326,12 +1366,15 @@
       <c r="H14" s="2">
         <v>73845</v>
       </c>
-      <c r="I14" s="2"/>
+      <c r="I14" s="2">
+        <v>11963</v>
+      </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -1356,12 +1399,15 @@
       <c r="H15" s="2">
         <v>38021</v>
       </c>
-      <c r="I15" s="2"/>
+      <c r="I15" s="2">
+        <v>6159</v>
+      </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
@@ -1386,12 +1432,15 @@
       <c r="H16" s="2">
         <v>45722</v>
       </c>
-      <c r="I16" s="2"/>
+      <c r="I16" s="2">
+        <v>7407</v>
+      </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
@@ -1416,12 +1465,15 @@
       <c r="H17" s="2">
         <v>43153</v>
       </c>
-      <c r="I17" s="2"/>
+      <c r="I17" s="2">
+        <v>6991</v>
+      </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
@@ -1446,21 +1498,24 @@
       <c r="H18" s="5">
         <v>1545</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="5">
+        <v>250</v>
+      </c>
+      <c r="J18" s="2">
         <v>4</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="K18" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K18" s="5">
+      <c r="L18" s="5">
         <v>250</v>
       </c>
-      <c r="L18" s="2">
+      <c r="M18" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:13">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -1485,21 +1540,24 @@
       <c r="H19" s="5">
         <v>2057</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19" s="5">
+        <v>333</v>
+      </c>
+      <c r="J19" s="2">
         <v>4</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="K19" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K19" s="5">
+      <c r="L19" s="5">
         <v>333</v>
       </c>
-      <c r="L19" s="2">
+      <c r="M19" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:13">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -1524,21 +1582,24 @@
       <c r="H20" s="5">
         <v>1727</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20" s="5">
+        <v>278</v>
+      </c>
+      <c r="J20" s="2">
         <v>4</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="K20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K20" s="5">
+      <c r="L20" s="5">
         <v>278</v>
       </c>
-      <c r="L20" s="2">
+      <c r="M20" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
@@ -1563,21 +1624,24 @@
       <c r="H21" s="5">
         <v>1867</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21" s="5">
+        <v>302</v>
+      </c>
+      <c r="J21" s="2">
         <v>4</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="K21" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K21" s="5">
+      <c r="L21" s="5">
         <v>302</v>
       </c>
-      <c r="L21" s="2">
+      <c r="M21" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:13">
       <c r="A22" s="2" t="s">
         <v>7</v>
       </c>
@@ -1602,21 +1666,24 @@
       <c r="H22" s="5">
         <v>1858</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22" s="5">
+        <v>301</v>
+      </c>
+      <c r="J22" s="2">
         <v>3</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="K22" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K22" s="5">
+      <c r="L22" s="5">
         <v>301</v>
       </c>
-      <c r="L22" s="2">
+      <c r="M22" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:13">
       <c r="A23" s="2" t="s">
         <v>7</v>
       </c>
@@ -1641,21 +1708,24 @@
       <c r="H23" s="5">
         <v>2184</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="5">
+        <v>353</v>
+      </c>
+      <c r="J23" s="2">
         <v>3</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="K23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K23" s="5">
+      <c r="L23" s="5">
         <v>353</v>
       </c>
-      <c r="L23" s="2">
+      <c r="M23" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:13">
       <c r="A24" s="2" t="s">
         <v>7</v>
       </c>
@@ -1680,21 +1750,24 @@
       <c r="H24" s="5">
         <v>4167</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24" s="5">
+        <v>674</v>
+      </c>
+      <c r="J24" s="2">
         <v>3</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="K24" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="K24" s="5">
+      <c r="L24" s="5">
         <v>674</v>
       </c>
-      <c r="L24" s="2">
+      <c r="M24" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:13">
       <c r="A25" s="2" t="s">
         <v>7</v>
       </c>
@@ -1719,12 +1792,15 @@
       <c r="H25" s="2">
         <v>71256</v>
       </c>
-      <c r="I25" s="2"/>
+      <c r="I25" s="2">
+        <v>11543</v>
+      </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="M25" s="2"/>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="2" t="s">
         <v>7</v>
       </c>
@@ -1749,21 +1825,24 @@
       <c r="H26" s="6">
         <v>5938</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26" s="5">
+        <v>962</v>
+      </c>
+      <c r="J26" s="2">
         <v>4</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="K26" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K26" s="5">
+      <c r="L26" s="5">
         <v>962</v>
       </c>
-      <c r="L26" s="2">
+      <c r="M26" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:13">
       <c r="A27" s="2" t="s">
         <v>7</v>
       </c>
@@ -1788,21 +1867,24 @@
       <c r="H27" s="6">
         <v>3340</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27" s="5">
+        <v>541</v>
+      </c>
+      <c r="J27" s="2">
         <v>4</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="K27" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="K27" s="5">
+      <c r="L27" s="5">
         <v>541</v>
       </c>
-      <c r="L27" s="2">
+      <c r="M27" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:13">
       <c r="A28" s="2" t="s">
         <v>7</v>
       </c>
@@ -1828,20 +1910,23 @@
         <v>79654</v>
       </c>
       <c r="I28" s="2">
+        <v>12904</v>
+      </c>
+      <c r="J28" s="2">
         <v>4</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="K28" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="K28" s="2">
+      <c r="L28" s="2">
         <v>12904</v>
       </c>
-      <c r="L28" s="2">
+      <c r="M28" s="2">
         <f t="shared" si="0"/>
         <v>462</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:13">
       <c r="A29" s="2" t="s">
         <v>7</v>
       </c>
@@ -1866,21 +1951,24 @@
       <c r="H29" s="5">
         <v>2339</v>
       </c>
-      <c r="I29" s="2">
+      <c r="I29" s="5">
+        <v>379</v>
+      </c>
+      <c r="J29" s="2">
         <v>4</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="K29" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="K29" s="5">
+      <c r="L29" s="5">
         <v>379</v>
       </c>
-      <c r="L29" s="2">
+      <c r="M29" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:13">
       <c r="A30" s="2" t="s">
         <v>7</v>
       </c>
@@ -1905,12 +1993,15 @@
       <c r="H30" s="2">
         <v>84872</v>
       </c>
-      <c r="I30" s="2"/>
+      <c r="I30" s="2">
+        <v>13749</v>
+      </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="M30" s="2"/>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="2" t="s">
         <v>7</v>
       </c>
@@ -1935,12 +2026,15 @@
       <c r="H31" s="2">
         <v>26067</v>
       </c>
-      <c r="I31" s="2"/>
+      <c r="I31" s="2">
+        <v>4223</v>
+      </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
-    </row>
-    <row r="32" spans="1:12">
+      <c r="M31" s="2"/>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="2" t="s">
         <v>7</v>
       </c>
@@ -1965,12 +2059,15 @@
       <c r="H32" s="2">
         <v>77639</v>
       </c>
-      <c r="I32" s="2"/>
+      <c r="I32" s="2">
+        <v>12577</v>
+      </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
-    </row>
-    <row r="33" spans="1:12">
+      <c r="M32" s="2"/>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="2" t="s">
         <v>7</v>
       </c>
@@ -1995,21 +2092,24 @@
       <c r="H33" s="5">
         <v>6610</v>
       </c>
-      <c r="I33" s="2">
+      <c r="I33" s="5">
+        <v>1069</v>
+      </c>
+      <c r="J33" s="2">
         <v>4</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="K33" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="K33" s="5">
+      <c r="L33" s="5">
         <v>1069</v>
       </c>
-      <c r="L33" s="2">
+      <c r="M33" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:13">
       <c r="A34" s="2" t="s">
         <v>7</v>
       </c>
@@ -2034,21 +2134,24 @@
       <c r="H34" s="5">
         <v>2878</v>
       </c>
-      <c r="I34" s="2">
+      <c r="I34" s="5">
+        <v>466</v>
+      </c>
+      <c r="J34" s="2">
         <v>4</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="K34" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K34" s="5">
+      <c r="L34" s="5">
         <v>466</v>
       </c>
-      <c r="L34" s="2">
+      <c r="M34" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:13">
       <c r="A35" s="2" t="s">
         <v>7</v>
       </c>
@@ -2073,21 +2176,24 @@
       <c r="H35" s="5">
         <v>3758</v>
       </c>
-      <c r="I35" s="2">
+      <c r="I35" s="5">
+        <v>608</v>
+      </c>
+      <c r="J35" s="2">
         <v>4</v>
       </c>
-      <c r="J35" s="2" t="s">
+      <c r="K35" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="K35" s="5">
+      <c r="L35" s="5">
         <v>608</v>
       </c>
-      <c r="L35" s="2">
+      <c r="M35" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:13">
       <c r="A36" s="2" t="s">
         <v>7</v>
       </c>
@@ -2112,21 +2218,24 @@
       <c r="H36" s="5">
         <v>3658</v>
       </c>
-      <c r="I36" s="2">
+      <c r="I36" s="5">
+        <v>591</v>
+      </c>
+      <c r="J36" s="2">
         <v>4</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="K36" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="K36" s="5">
+      <c r="L36" s="5">
         <v>591</v>
       </c>
-      <c r="L36" s="2">
+      <c r="M36" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:13">
       <c r="A37" s="2" t="s">
         <v>7</v>
       </c>
@@ -2151,12 +2260,15 @@
       <c r="H37" s="2">
         <v>104918</v>
       </c>
-      <c r="I37" s="2"/>
+      <c r="I37" s="2">
+        <v>16997</v>
+      </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
-    </row>
-    <row r="38" spans="1:12">
+      <c r="M37" s="2"/>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="2" t="s">
         <v>7</v>
       </c>
@@ -2179,8 +2291,9 @@
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="1:12">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="2" t="s">
         <v>7</v>
       </c>
@@ -2205,12 +2318,15 @@
       <c r="H39" s="2">
         <v>31271</v>
       </c>
-      <c r="I39" s="2"/>
+      <c r="I39" s="2">
+        <v>5066</v>
+      </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
-    </row>
-    <row r="40" spans="1:12">
+      <c r="M39" s="2"/>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="2" t="s">
         <v>7</v>
       </c>
@@ -2235,12 +2351,15 @@
       <c r="H40" s="2">
         <v>31271</v>
       </c>
-      <c r="I40" s="2"/>
+      <c r="I40" s="2">
+        <v>5066</v>
+      </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
-    </row>
-    <row r="41" spans="1:12">
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="2" t="s">
         <v>7</v>
       </c>
@@ -2265,21 +2384,24 @@
       <c r="H41" s="5">
         <v>950</v>
       </c>
-      <c r="I41" s="2">
+      <c r="I41" s="5">
+        <v>153</v>
+      </c>
+      <c r="J41" s="2">
         <v>3</v>
       </c>
-      <c r="J41" s="2" t="s">
+      <c r="K41" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K41" s="5">
+      <c r="L41" s="5">
         <v>153</v>
       </c>
-      <c r="L41" s="2">
+      <c r="M41" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:13">
       <c r="A42" s="2" t="s">
         <v>7</v>
       </c>
@@ -2304,21 +2426,24 @@
       <c r="H42" s="5">
         <v>2624</v>
       </c>
-      <c r="I42" s="2">
+      <c r="I42" s="5">
+        <v>425</v>
+      </c>
+      <c r="J42" s="2">
         <v>3</v>
       </c>
-      <c r="J42" s="2" t="s">
+      <c r="K42" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="K42" s="5">
+      <c r="L42" s="5">
         <v>425</v>
       </c>
-      <c r="L42" s="2">
+      <c r="M42" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:13">
       <c r="A43" s="2" t="s">
         <v>7</v>
       </c>
@@ -2343,21 +2468,24 @@
       <c r="H43" s="5">
         <v>1967</v>
       </c>
-      <c r="I43" s="2">
+      <c r="I43" s="5">
+        <v>318</v>
+      </c>
+      <c r="J43" s="2">
         <v>3</v>
       </c>
-      <c r="J43" s="2" t="s">
+      <c r="K43" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="K43" s="5">
+      <c r="L43" s="5">
         <v>318</v>
       </c>
-      <c r="L43" s="2">
+      <c r="M43" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:13">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
@@ -2382,12 +2510,15 @@
       <c r="H44" s="2">
         <v>52709</v>
       </c>
-      <c r="I44" s="2"/>
+      <c r="I44" s="2">
+        <v>8539</v>
+      </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
-    </row>
-    <row r="45" spans="1:12">
+      <c r="M44" s="2"/>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="2" t="s">
         <v>7</v>
       </c>
@@ -2412,12 +2543,15 @@
       <c r="H45" s="2">
         <v>39823</v>
       </c>
-      <c r="I45" s="2"/>
+      <c r="I45" s="2">
+        <v>6451</v>
+      </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
-    </row>
-    <row r="46" spans="1:12">
+      <c r="M45" s="2"/>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="2" t="s">
         <v>7</v>
       </c>
@@ -2442,21 +2576,24 @@
       <c r="H46" s="5">
         <v>1541</v>
       </c>
-      <c r="I46" s="2">
+      <c r="I46" s="5">
+        <v>250</v>
+      </c>
+      <c r="J46" s="2">
         <v>3</v>
       </c>
-      <c r="J46" s="2" t="s">
+      <c r="K46" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="K46" s="5">
+      <c r="L46" s="5">
         <v>250</v>
       </c>
-      <c r="L46" s="2">
+      <c r="M46" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:13">
       <c r="A47" s="2" t="s">
         <v>7</v>
       </c>
@@ -2481,21 +2618,24 @@
       <c r="H47" s="5">
         <v>872</v>
       </c>
-      <c r="I47" s="2">
+      <c r="I47" s="5">
+        <v>141</v>
+      </c>
+      <c r="J47" s="2">
         <v>3</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="K47" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="K47" s="5">
+      <c r="L47" s="5">
         <v>141</v>
       </c>
-      <c r="L47" s="2">
+      <c r="M47" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:13">
       <c r="A48" s="2" t="s">
         <v>7</v>
       </c>
@@ -2520,21 +2660,24 @@
       <c r="H48" s="5">
         <v>3487</v>
       </c>
-      <c r="I48" s="2">
+      <c r="I48" s="5">
+        <v>565</v>
+      </c>
+      <c r="J48" s="2">
         <v>3</v>
       </c>
-      <c r="J48" s="2" t="s">
+      <c r="K48" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="K48" s="5">
+      <c r="L48" s="5">
         <v>565</v>
       </c>
-      <c r="L48" s="2">
+      <c r="M48" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:13">
       <c r="A49" s="2" t="s">
         <v>7</v>
       </c>
@@ -2559,21 +2702,24 @@
       <c r="H49" s="5">
         <v>3933</v>
       </c>
-      <c r="I49" s="2">
-        <v>7</v>
-      </c>
-      <c r="J49" s="2" t="s">
+      <c r="I49" s="7">
+        <v>654</v>
+      </c>
+      <c r="J49" s="2">
+        <v>7</v>
+      </c>
+      <c r="K49" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="K49" s="7">
+      <c r="L49" s="7">
         <v>654</v>
       </c>
-      <c r="L49" s="2">
+      <c r="M49" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:13">
       <c r="A50" s="2" t="s">
         <v>7</v>
       </c>
@@ -2598,21 +2744,24 @@
       <c r="H50" s="5">
         <v>7519</v>
       </c>
-      <c r="I50" s="2">
-        <v>7</v>
-      </c>
-      <c r="J50" s="2" t="s">
+      <c r="I50" s="5">
+        <v>1249</v>
+      </c>
+      <c r="J50" s="2">
+        <v>7</v>
+      </c>
+      <c r="K50" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K50" s="5">
+      <c r="L50" s="5">
         <v>1249</v>
       </c>
-      <c r="L50" s="2">
+      <c r="M50" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:13">
       <c r="A51" s="2" t="s">
         <v>7</v>
       </c>
@@ -2637,21 +2786,24 @@
       <c r="H51" s="5">
         <v>4245</v>
       </c>
-      <c r="I51" s="2">
-        <v>7</v>
-      </c>
-      <c r="J51" s="2" t="s">
+      <c r="I51" s="5">
+        <v>705</v>
+      </c>
+      <c r="J51" s="2">
+        <v>7</v>
+      </c>
+      <c r="K51" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="K51" s="5">
+      <c r="L51" s="5">
         <v>705</v>
       </c>
-      <c r="L51" s="2">
+      <c r="M51" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:13">
       <c r="A52" s="2" t="s">
         <v>7</v>
       </c>
@@ -2676,21 +2828,24 @@
       <c r="H52" s="5">
         <v>736</v>
       </c>
-      <c r="I52" s="2">
-        <v>7</v>
-      </c>
-      <c r="J52" s="2" t="s">
+      <c r="I52" s="5">
+        <v>122</v>
+      </c>
+      <c r="J52" s="2">
+        <v>7</v>
+      </c>
+      <c r="K52" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="K52" s="5">
+      <c r="L52" s="5">
         <v>122</v>
       </c>
-      <c r="L52" s="2">
+      <c r="M52" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:13">
       <c r="A53" s="2" t="s">
         <v>7</v>
       </c>
@@ -2715,21 +2870,24 @@
       <c r="H53" s="5">
         <v>832</v>
       </c>
-      <c r="I53" s="2">
-        <v>7</v>
-      </c>
-      <c r="J53" s="2" t="s">
+      <c r="I53" s="5">
+        <v>138</v>
+      </c>
+      <c r="J53" s="2">
+        <v>7</v>
+      </c>
+      <c r="K53" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="K53" s="5">
+      <c r="L53" s="5">
         <v>138</v>
       </c>
-      <c r="L53" s="2">
+      <c r="M53" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:13">
       <c r="A54" s="2" t="s">
         <v>7</v>
       </c>
@@ -2754,21 +2912,24 @@
       <c r="H54" s="5">
         <v>2982</v>
       </c>
-      <c r="I54" s="2">
-        <v>7</v>
-      </c>
-      <c r="J54" s="2" t="s">
+      <c r="I54" s="5">
+        <v>495</v>
+      </c>
+      <c r="J54" s="2">
+        <v>7</v>
+      </c>
+      <c r="K54" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K54" s="5">
+      <c r="L54" s="5">
         <v>495</v>
       </c>
-      <c r="L54" s="2">
+      <c r="M54" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:13">
       <c r="A55" s="2" t="s">
         <v>7</v>
       </c>
@@ -2793,22 +2954,25 @@
       <c r="H55" s="5">
         <v>960</v>
       </c>
-      <c r="I55" s="2">
-        <v>7</v>
-      </c>
-      <c r="J55" s="2" t="s">
+      <c r="I55" s="5">
+        <v>160</v>
+      </c>
+      <c r="J55" s="2">
+        <v>7</v>
+      </c>
+      <c r="K55" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="K55" s="5">
+      <c r="L55" s="5">
         <v>160</v>
       </c>
-      <c r="L55" s="2">
+      <c r="M55" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
-      <c r="L56" s="8"/>
+    <row r="56" spans="1:13">
+      <c r="M56" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/population.xlsx
+++ b/population.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b00e9cd42f584bf2/Documents/Population visualizer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8C3DDF4-0BCF-481A-B792-0BFDE3217C84}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="11_2068ABE58CA14257F81ACF531E6AA93484635D3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A898742-DB76-40D4-86E8-682F1B9A6FC9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -893,8 +893,8 @@
         <v>1151</v>
       </c>
       <c r="M2" s="2">
-        <f>ROUND((SUM(1267*L2)/35362)+0.08,0)</f>
-        <v>41</v>
+        <f>ROUND((SUM(1267*L2)/32938)-0.0785,0)</f>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -935,8 +935,8 @@
         <v>2305</v>
       </c>
       <c r="M3" s="2">
-        <f t="shared" ref="M3:M55" si="0">ROUND((SUM(1267*L3)/35362)+0.08,0)</f>
-        <v>83</v>
+        <f t="shared" ref="M3:M55" si="0">ROUND((SUM(1267*L3)/32938)-0.0785,0)</f>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="M5" s="2">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="M7" s="2">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="M8" s="2">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="M9" s="2">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M10" s="2">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="M11" s="2">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="M12" s="2">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="M18" s="2">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M19" s="2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="M20" s="2">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="M21" s="2">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="M23" s="2">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M24" s="2">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="M26" s="2">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="M27" s="2">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="M28" s="2">
         <f t="shared" si="0"/>
-        <v>462</v>
+        <v>496</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="M29" s="2">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="M33" s="2">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="M34" s="2">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="M35" s="2">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="M36" s="2">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="M42" s="2">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="M43" s="2">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="M46" s="2">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M48" s="2">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="M49" s="2">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="M50" s="2">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="M51" s="2">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="M52" s="2">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="M54" s="2">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:13">
